--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -56992,7 +56992,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -151,12 +151,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -233,12 +233,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -315,12 +315,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -479,12 +479,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -561,12 +561,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -725,12 +725,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -807,12 +807,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -889,12 +889,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1053,12 +1053,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1217,12 +1217,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1299,12 +1299,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1463,12 +1463,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1709,12 +1709,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1955,12 +1955,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2037,12 +2037,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2114,12 +2114,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2191,12 +2191,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -57024,12 +57024,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -161,7 +161,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -171,12 +171,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -186,17 +186,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -226,7 +226,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-2</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -243,7 +243,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -253,12 +253,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -268,17 +268,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -298,7 +298,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -308,7 +308,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-3</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -325,7 +325,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -335,12 +335,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -350,17 +350,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -380,7 +380,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -390,7 +390,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-4</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -407,7 +407,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -417,12 +417,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -432,17 +432,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-5</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -514,17 +514,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-6</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-7</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -678,17 +678,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-09-04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -718,7 +713,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-8</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -735,7 +730,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -745,12 +740,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -760,17 +755,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-09-04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -800,7 +790,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-9</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -817,7 +807,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -827,12 +817,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -842,17 +832,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-09-04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -882,7 +867,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-10</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -899,7 +884,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -909,12 +894,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -924,12 +909,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-08-06</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">06.08.20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -964,7 +949,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-11</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -981,7 +966,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -991,12 +976,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1006,12 +991,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-08-06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">06.08.20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1046,7 +1031,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-12</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1048,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1073,12 +1058,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1088,17 +1073,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1108,7 +1093,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1128,7 +1113,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-13</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1130,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1155,12 +1140,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1170,17 +1155,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1190,7 +1175,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1210,7 +1195,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-14</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1212,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1237,12 +1222,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,17 +1237,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1272,7 +1257,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1292,7 +1277,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-15</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1294,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1319,12 +1304,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1334,17 +1319,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1354,7 +1339,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1374,7 +1359,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-16</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1376,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1401,12 +1386,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1416,17 +1401,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1436,7 +1421,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1456,7 +1441,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-17</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1458,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1483,12 +1468,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1498,17 +1483,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.12.19</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1518,7 +1503,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1538,7 +1523,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-18</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1540,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1565,32 +1550,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.12.19</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1600,7 +1580,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1620,7 +1600,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-19</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1617,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1647,32 +1627,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1682,7 +1657,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1702,7 +1677,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-20</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1694,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1729,32 +1704,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1764,7 +1739,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1784,7 +1759,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-21</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1776,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1811,32 +1786,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1846,7 +1821,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1866,7 +1841,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-22</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1858,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1893,32 +1868,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1948,7 +1923,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-23</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1940,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1975,32 +1950,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2030,7 +2005,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-24</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2022,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2057,12 +2032,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
+          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">46.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2072,12 +2047,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve">2020-07-16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.01.20</t>
+          <t xml:space="preserve">16.07.20</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2107,7 +2087,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-25</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2104,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2134,12 +2114,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">79.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2149,12 +2129,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.01.20</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2184,7 +2164,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-26</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2181,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2211,12 +2191,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P80 27.1.20 BARO</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2226,12 +2206,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.01.20</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2261,19 +2241,19 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-27</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2283,17 +2263,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2303,17 +2283,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2333,7 +2308,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2343,19 +2318,19 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2365,17 +2340,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
+          <t xml:space="preserve">U373 P84 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">84.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2385,17 +2360,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2415,7 +2385,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2425,19 +2395,19 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2447,17 +2417,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
+          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2467,17 +2437,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">31.07.20</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2497,7 +2462,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2507,19 +2472,19 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2529,17 +2494,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">52.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2549,17 +2514,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2569,7 +2534,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2579,7 +2544,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2589,19 +2554,19 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2611,17 +2576,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">52.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2631,17 +2596,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2651,7 +2616,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2661,7 +2626,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2671,19 +2636,19 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2693,17 +2658,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2713,17 +2678,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2733,7 +2698,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2743,7 +2708,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2753,19 +2718,19 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2775,17 +2740,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2795,12 +2760,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-04</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2810,7 +2780,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2830,19 +2800,19 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2852,17 +2822,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2872,12 +2842,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-04</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2907,19 +2882,19 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2929,17 +2904,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2949,12 +2924,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-04</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2984,19 +2964,19 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3006,17 +2986,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3026,17 +3006,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-06</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">06.08.20</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3066,19 +3041,19 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3088,17 +3063,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3108,17 +3083,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-06</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">06.08.20</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3148,19 +3118,19 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3170,17 +3140,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3190,17 +3160,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3210,7 +3175,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3230,19 +3195,19 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3252,17 +3217,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">77.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3272,17 +3237,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3292,7 +3252,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3312,19 +3272,19 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3334,17 +3294,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">U373 P85 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">85.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3354,17 +3314,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3374,7 +3329,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3394,19 +3349,19 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3416,17 +3371,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">29.0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3436,17 +3391,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3456,7 +3411,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3476,19 +3431,19 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3498,17 +3453,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">36.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3518,17 +3473,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3538,7 +3493,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3558,19 +3513,19 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3580,37 +3535,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-03-13</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3620,7 +3570,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3640,19 +3590,19 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3662,12 +3612,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3682,12 +3632,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-03-13</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3717,19 +3667,19 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3739,32 +3689,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3774,7 +3724,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3794,19 +3744,19 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3816,37 +3766,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3856,7 +3801,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3876,19 +3821,19 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3898,37 +3843,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3938,7 +3878,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3958,19 +3898,19 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3980,37 +3920,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">77.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4040,19 +3975,19 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4062,37 +3997,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4122,19 +4057,19 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4144,17 +4079,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">46.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4164,17 +4099,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-16</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4204,19 +4139,19 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4226,17 +4161,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">79.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4246,12 +4181,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4281,19 +4221,19 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4303,17 +4243,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4323,12 +4263,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4358,19 +4303,19 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4380,17 +4325,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4400,12 +4345,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4435,19 +4385,19 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4457,17 +4407,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P84 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">84.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4477,12 +4427,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4512,7 +4467,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -4529,22 +4484,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4554,12 +4509,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-31</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.07.20</t>
+          <t xml:space="preserve">10.02.20</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4589,7 +4549,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-2</t>
         </is>
       </c>
     </row>
@@ -4606,22 +4566,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4631,17 +4591,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4651,7 +4611,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4671,7 +4631,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-3</t>
         </is>
       </c>
     </row>
@@ -4688,22 +4648,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4713,17 +4673,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4733,7 +4693,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4753,7 +4713,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-4</t>
         </is>
       </c>
     </row>
@@ -4770,22 +4730,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4795,17 +4755,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4815,7 +4775,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4835,7 +4795,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-5</t>
         </is>
       </c>
     </row>
@@ -4852,22 +4812,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4877,17 +4837,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4897,7 +4857,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4917,7 +4877,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-6</t>
         </is>
       </c>
     </row>
@@ -4934,22 +4894,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4959,17 +4919,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4999,7 +4959,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-7</t>
         </is>
       </c>
     </row>
@@ -5016,22 +4976,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5041,17 +5001,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5081,7 +5041,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-8</t>
         </is>
       </c>
     </row>
@@ -5098,22 +5058,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5123,12 +5083,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">15.12.19</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5158,7 +5123,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-9</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5140,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5200,12 +5165,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">14.12.19</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5235,7 +5205,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-10</t>
         </is>
       </c>
     </row>
@@ -5252,22 +5222,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5277,12 +5247,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">14.12.19</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5312,7 +5287,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-11</t>
         </is>
       </c>
     </row>
@@ -5329,22 +5304,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5354,12 +5329,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">14.12.19</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5389,7 +5369,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-12</t>
         </is>
       </c>
     </row>
@@ -5406,22 +5386,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P85 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">85.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5431,12 +5411,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">14.12.19</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5466,7 +5451,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-13</t>
         </is>
       </c>
     </row>
@@ -5483,22 +5468,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5508,12 +5493,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-17</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.20</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5548,7 +5533,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-14</t>
         </is>
       </c>
     </row>
@@ -5565,22 +5550,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC)</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5590,12 +5575,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-17</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5630,7 +5615,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-15</t>
         </is>
       </c>
     </row>
@@ -5647,37 +5632,42 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-13</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.20</t>
+          <t xml:space="preserve">10.02.20</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5687,7 +5677,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5707,7 +5697,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-16</t>
         </is>
       </c>
     </row>
@@ -5724,37 +5714,42 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-13</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.20</t>
+          <t xml:space="preserve">10.02.20</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5764,7 +5759,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5784,7 +5779,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-17</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5796,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">25.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5826,12 +5821,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">22.12.19</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-18</t>
         </is>
       </c>
     </row>
@@ -5878,22 +5878,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">25.0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5903,12 +5903,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">22.12.19</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5938,7 +5943,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-19</t>
         </is>
       </c>
     </row>
@@ -5955,22 +5960,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5980,12 +5985,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">01.01.20</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6015,7 +6025,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-20</t>
         </is>
       </c>
     </row>
@@ -6032,22 +6042,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6057,12 +6067,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">01.01.20</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6092,7 +6107,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-21</t>
         </is>
       </c>
     </row>
@@ -6109,22 +6124,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6134,17 +6149,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6174,7 +6189,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-22</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6206,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6216,17 +6231,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6256,7 +6271,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-23</t>
         </is>
       </c>
     </row>
@@ -6273,22 +6288,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6298,17 +6313,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6338,7 +6353,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-24</t>
         </is>
       </c>
     </row>
@@ -6355,22 +6370,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6380,17 +6395,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-27</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6420,7 +6430,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-25</t>
         </is>
       </c>
     </row>
@@ -6437,22 +6447,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6462,17 +6472,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-27</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6502,7 +6507,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-26</t>
         </is>
       </c>
     </row>
@@ -6519,22 +6524,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">U373 P80 27.1.20 BARO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6544,17 +6549,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-27</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-27</t>
         </is>
       </c>
     </row>
@@ -57034,7 +57034,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -57052,10 +57052,10 @@
         <v>81</v>
       </c>
       <c r="I8">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J8">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -57071,7 +57071,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -57089,10 +57089,10 @@
         <v>81</v>
       </c>
       <c r="I9">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J9">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -161,7 +161,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -171,32 +171,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR fluc-mCherry SORTED 28.04.21 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-28</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.04.21</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -226,7 +226,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-164</t>
+          <t xml:space="preserve">v-2</t>
         </is>
       </c>
     </row>
@@ -243,7 +243,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -253,32 +253,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR flucmCherry SORTED 28.04.21 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-28</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.04.21</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -288,7 +288,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -308,7 +308,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-165</t>
+          <t xml:space="preserve">v-3</t>
         </is>
       </c>
     </row>
@@ -325,7 +325,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -335,27 +335,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR flucmCherry SORTED 28.04.21 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-28</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.04.21</t>
+          <t xml:space="preserve">10.02.20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -365,7 +370,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -385,7 +390,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-166</t>
+          <t xml:space="preserve">v-4</t>
         </is>
       </c>
     </row>
@@ -402,7 +407,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -412,32 +417,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR flucmCherry SORTED 28.04.21 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-28</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.04.21</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -447,7 +452,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -467,7 +472,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-167</t>
+          <t xml:space="preserve">v-5</t>
         </is>
       </c>
     </row>
@@ -484,7 +489,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -494,32 +499,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR SIRT1 28.04.21 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-28</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.04.21</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -529,7 +534,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -549,7 +554,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-168</t>
+          <t xml:space="preserve">v-6</t>
         </is>
       </c>
     </row>
@@ -566,7 +571,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -576,32 +581,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR SIRT1 28.04.21 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-28</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.04.21</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -611,7 +616,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -631,7 +636,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-169</t>
+          <t xml:space="preserve">v-7</t>
         </is>
       </c>
     </row>
@@ -648,7 +653,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -658,12 +663,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 SIRT1 (retro) P81 29.03.21 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">81.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -673,17 +678,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.03.21</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -713,7 +718,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-170</t>
+          <t xml:space="preserve">v-8</t>
         </is>
       </c>
     </row>
@@ -730,7 +735,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -740,12 +745,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa P31 29.03.21 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -755,12 +760,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.03.21</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -795,7 +800,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-171</t>
+          <t xml:space="preserve">v-9</t>
         </is>
       </c>
     </row>
@@ -812,7 +817,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -822,12 +827,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145-Ki PC P81 11.06.21 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">81.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -837,17 +842,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-11</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.06.21</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-172</t>
+          <t xml:space="preserve">v-10</t>
         </is>
       </c>
     </row>
@@ -894,7 +899,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -904,12 +909,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -919,17 +924,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.03.21</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-173</t>
+          <t xml:space="preserve">v-11</t>
         </is>
       </c>
     </row>
@@ -976,7 +981,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -986,12 +991,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1001,17 +1006,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.03.21</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1041,7 +1046,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-174</t>
+          <t xml:space="preserve">v-12</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1063,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1068,12 +1073,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1083,17 +1088,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.03.21</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1123,7 +1128,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-175</t>
+          <t xml:space="preserve">v-13</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1145,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1150,12 +1155,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1165,17 +1170,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.03.21</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1205,7 +1210,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-176</t>
+          <t xml:space="preserve">v-14</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1227,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1232,12 +1237,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1247,17 +1252,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.03.21</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1292,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-177</t>
+          <t xml:space="preserve">v-15</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1309,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1314,12 +1319,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #10 P19+10 07.06.21</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+10</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1329,17 +1334,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-07</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">07.06.21</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1369,7 +1374,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-178</t>
+          <t xml:space="preserve">v-16</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1396,12 +1401,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #1 P19+10 07.06.21</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+10</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1411,17 +1416,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-07</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">07.06.21</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1451,7 +1456,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-179</t>
+          <t xml:space="preserve">v-17</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1473,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1478,12 +1483,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #3 P19+10 07.06.21</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+10</t>
+          <t xml:space="preserve">25.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1493,17 +1498,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-07</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">07.06.21</t>
+          <t xml:space="preserve">22.12.19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1533,7 +1538,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-180</t>
+          <t xml:space="preserve">v-18</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1555,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1560,12 +1565,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #12 P19+10 07.06.21</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+10</t>
+          <t xml:space="preserve">25.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1575,17 +1580,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-07</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">07.06.21</t>
+          <t xml:space="preserve">22.12.19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1615,7 +1620,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-181</t>
+          <t xml:space="preserve">v-19</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1637,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1642,12 +1647,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #9 P19+10 07.06.21</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+10</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1657,17 +1662,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-07</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">07.06.21</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1697,7 +1702,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-182</t>
+          <t xml:space="preserve">v-20</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1719,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1724,12 +1729,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-10CR P106 13.07.21</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">106.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1739,17 +1744,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-07-13</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.07.21</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1779,7 +1784,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-183</t>
+          <t xml:space="preserve">v-21</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1801,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1806,12 +1811,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-10CR P106 13.07.21</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">106.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1821,17 +1826,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-07-13</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.07.21</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1861,7 +1866,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-184</t>
+          <t xml:space="preserve">v-22</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1883,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1888,7 +1893,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panc1 P24 26.12.19</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1903,12 +1908,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-26</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.12.19</t>
+          <t xml:space="preserve">01.01.20</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1938,7 +1948,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-185</t>
+          <t xml:space="preserve">v-23</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1965,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1965,12 +1975,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">99.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1978,14 +1988,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-01-01</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1995,7 +2010,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2015,7 +2030,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-186</t>
+          <t xml:space="preserve">v-24</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2047,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2042,12 +2057,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panc1 P24 26.12.19</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2055,9 +2070,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-01-27</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2087,7 +2107,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-187</t>
+          <t xml:space="preserve">v-25</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2124,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2114,12 +2134,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">134.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2127,14 +2147,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-01-27</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2144,7 +2164,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2164,7 +2184,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-188</t>
+          <t xml:space="preserve">v-26</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2201,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2191,12 +2211,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21</t>
+          <t xml:space="preserve">U373 P80 27.1.20 BARO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">99.0</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2204,14 +2224,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-01-27</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2221,7 +2241,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2241,7 +2261,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-189</t>
+          <t xml:space="preserve">v-27</t>
         </is>
       </c>
     </row>
@@ -2258,22 +2278,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P84 12.07.21 BARO</t>
+          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">84.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2281,14 +2301,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-12-17</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2298,7 +2323,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2308,7 +2333,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2318,7 +2343,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-190</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -2335,22 +2360,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P40 29.04.22 BARO</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">40.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2358,14 +2383,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-12-17</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2385,7 +2415,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2395,7 +2425,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-191</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -2412,22 +2442,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P45 04.10.21 BARO</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">45.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2435,14 +2465,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-12-17</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2462,7 +2497,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2472,7 +2507,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-192</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -2489,22 +2524,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-CR 1x15uM recovered P110 19.08.21 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">110.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2512,14 +2547,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-12-17</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2539,7 +2579,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2549,7 +2589,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-193</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -2566,22 +2606,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-1x15CR P111 19.08.21</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">111.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2589,14 +2629,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-12-17</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2606,7 +2651,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2616,7 +2661,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2626,7 +2671,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-194</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -2643,22 +2688,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2x15CR P112 13.09.21</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">112.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2666,14 +2711,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-12-17</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2683,7 +2733,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2693,7 +2743,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2703,7 +2753,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-195</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -2720,22 +2770,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR p134 15.04.22</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">134.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2743,14 +2793,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-09-04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2780,7 +2830,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-196</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -2797,37 +2847,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #11 18.07.21</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-09-04</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2857,7 +2907,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-197</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -2874,37 +2924,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #31 18.07.21</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-09-04</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2934,7 +2984,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-198</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -2951,37 +3001,42 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #32 18.07.21</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-06</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06.08.20</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3011,7 +3066,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-199</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -3028,37 +3083,42 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #20 18.07.21</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-06</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06.08.20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3088,7 +3148,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-200</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3165,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #25 18.07.21</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3145,7 +3210,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3165,7 +3230,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-201</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -3182,32 +3247,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #24 18.07.21</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3222,7 +3292,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3242,7 +3312,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-202</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -3259,32 +3329,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #18 18.07.21</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3299,7 +3374,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3319,7 +3394,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-203</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3411,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #22 18.07.21</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3376,7 +3456,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3396,7 +3476,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-204</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -3413,32 +3493,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #13 18.07.21</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3453,7 +3538,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3473,7 +3558,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-205</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -3490,32 +3575,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #3 18.07.21</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3530,7 +3620,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3550,7 +3640,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-206</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -3567,17 +3657,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #5 18.07.21</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3590,14 +3680,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3607,7 +3697,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3627,7 +3717,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-207</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -3644,17 +3734,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #8 18.07.21</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3667,14 +3757,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3684,7 +3774,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3704,7 +3794,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-208</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -3721,17 +3811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #9 18.07.21</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3744,14 +3834,19 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3761,7 +3856,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3781,7 +3876,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-209</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -3798,17 +3893,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #1 18.07.21</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3821,14 +3916,19 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3838,7 +3938,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3858,7 +3958,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-210</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -3875,17 +3975,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #26 18.07.21</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3898,14 +3998,19 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3935,7 +4040,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-211</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -3952,17 +4057,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #29 18.07.21</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3975,14 +4080,19 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4012,7 +4122,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-212</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -4029,37 +4139,42 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #21 18.07.21</t>
+          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">46.0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-16</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.07.20</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4089,7 +4204,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-213</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -4106,37 +4221,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #34 18.07.21</t>
+          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">79.0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-08</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4166,7 +4281,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-214</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -4183,37 +4298,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #4 18.07.21</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-08</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4243,7 +4358,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-215</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -4260,37 +4375,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #10 18.07.21</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-08</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4320,7 +4435,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-216</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -4337,22 +4452,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22 BARO</t>
+          <t xml:space="preserve">U373 P84 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">134.0</t>
+          <t xml:space="preserve">84.0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4360,14 +4475,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-08</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4377,7 +4492,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4397,7 +4512,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-217</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -4414,22 +4529,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2x20CR P130 25.02.22 BARO</t>
+          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">130.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4437,14 +4552,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-31</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.07.20</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4474,7 +4589,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-218</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -4491,22 +4606,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO</t>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">39.0</t>
+          <t xml:space="preserve">52.0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4514,9 +4629,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4526,7 +4651,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4546,7 +4671,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-219</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -4563,22 +4688,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO</t>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">39.0</t>
+          <t xml:space="preserve">52.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4586,9 +4711,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4598,7 +4733,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4618,7 +4753,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-220</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -4635,22 +4770,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCaP P15-Canada 14.10.21 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4658,14 +4793,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4675,7 +4815,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4695,7 +4835,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-221</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -4712,22 +4852,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">116.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4735,9 +4875,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4752,7 +4897,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4772,7 +4917,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-222</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -4789,22 +4934,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">116.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4812,9 +4957,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4829,7 +4979,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4849,7 +4999,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-223</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -4866,22 +5016,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">116.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4889,9 +5039,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-20</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4906,7 +5061,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4926,7 +5081,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-224</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -4943,22 +5098,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-1x25CR P122 30.03.22 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">122.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4966,14 +5121,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-14</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4983,7 +5138,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5003,7 +5158,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-225</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -5020,22 +5175,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">116.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5043,14 +5198,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-14</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5060,7 +5215,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5080,7 +5235,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-226</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -5097,37 +5252,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2 PX+11 02.10.21 BARO</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">X+11</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5157,7 +5312,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-227</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -5174,22 +5329,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 P32 23.10.21 BARO</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">32.0</t>
+          <t xml:space="preserve">77.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5197,14 +5352,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5234,7 +5389,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-228</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -5251,22 +5406,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-15CR* P122 16.12.21 BARO</t>
+          <t xml:space="preserve">U373 P85 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">122.0</t>
+          <t xml:space="preserve">85.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5274,14 +5429,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5311,7 +5466,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-229</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -5328,37 +5483,42 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-luc 30.03.22 Ayça</t>
+          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">29.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-02-17</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5388,7 +5548,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-230</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -5405,22 +5565,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 P32 23.10.21 BARO</t>
+          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">32.0</t>
+          <t xml:space="preserve">36.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5428,14 +5588,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-02-17</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5465,7 +5630,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-231</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -5482,17 +5647,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR-luc 30.03.22 Ayça</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5505,9 +5670,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-13</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5517,7 +5687,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5537,7 +5707,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-232</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -5554,37 +5724,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">116.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-13</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5614,7 +5784,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-233</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -5631,32 +5801,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">PC3 cell pellet</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-14</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5686,7 +5861,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-234</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -5703,32 +5878,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">PC3 cell pellet</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-14</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5758,7 +5938,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-235</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -5775,37 +5955,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCaP pellet</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5835,7 +6015,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-236</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -5852,37 +6032,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCaP pellet</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">77.0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5912,7 +6092,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-237</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -5929,32 +6109,42 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS pellet</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5984,7 +6174,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-238</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -6001,37 +6191,42 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 pellet</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6061,7 +6256,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-239</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -6078,32 +6273,42 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 pellet</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6133,7 +6338,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-240</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -6150,37 +6355,42 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2 pellet</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6210,7 +6420,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-241</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -6227,32 +6437,42 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-231 pellet</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6282,39 +6502,39 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-242</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6324,17 +6544,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6364,7 +6584,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-2</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -6381,42 +6601,42 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">22PAR fluc-mCherry SORTED 28.04.21 BARO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2021-04-28</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6446,7 +6666,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-3</t>
+          <t xml:space="preserve">v-164</t>
         </is>
       </c>
     </row>
@@ -6463,42 +6683,42 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">22DoceR flucmCherry SORTED 28.04.21 BARO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2021-04-28</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6508,7 +6728,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6528,7 +6748,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-4</t>
+          <t xml:space="preserve">v-165</t>
         </is>
       </c>
     </row>
@@ -6545,42 +6765,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">22CabaR flucmCherry SORTED 28.04.21 BARO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2021-04-28</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6590,7 +6805,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6610,7 +6825,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-5</t>
+          <t xml:space="preserve">v-166</t>
         </is>
       </c>
     </row>
@@ -6627,42 +6842,42 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">DuDoceR flucmCherry SORTED 28.04.21 BARO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2021-04-28</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6672,7 +6887,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6692,7 +6907,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-6</t>
+          <t xml:space="preserve">v-167</t>
         </is>
       </c>
     </row>
@@ -6709,42 +6924,42 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">DuDoceR SIRT1 28.04.21 BARO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2021-04-28</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6754,7 +6969,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6774,7 +6989,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-7</t>
+          <t xml:space="preserve">v-168</t>
         </is>
       </c>
     </row>
@@ -6791,42 +7006,42 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">DuCabaR SIRT1 28.04.21 BARO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2021-04-28</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6836,7 +7051,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6856,7 +7071,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-8</t>
+          <t xml:space="preserve">v-169</t>
         </is>
       </c>
     </row>
@@ -6873,22 +7088,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">Du145 SIRT1 (retro) P81 29.03.21 BARO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">81.0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6898,17 +7113,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">29.03.21</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6938,7 +7153,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-9</t>
+          <t xml:space="preserve">v-170</t>
         </is>
       </c>
     </row>
@@ -6955,22 +7170,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">HeLa P31 29.03.21 BARO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">31.0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6980,12 +7195,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">29.03.21</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7020,7 +7235,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-10</t>
+          <t xml:space="preserve">v-171</t>
         </is>
       </c>
     </row>
@@ -7037,22 +7252,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">Du145-Ki PC P81 11.06.21 BARO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">81.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7062,17 +7277,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2021-06-11</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">11.06.21</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7102,7 +7317,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-11</t>
+          <t xml:space="preserve">v-172</t>
         </is>
       </c>
     </row>
@@ -7119,22 +7334,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7144,17 +7359,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">29.03.21</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7184,7 +7399,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-12</t>
+          <t xml:space="preserve">v-173</t>
         </is>
       </c>
     </row>
@@ -7201,22 +7416,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7226,17 +7441,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">29.03.21</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7266,7 +7481,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-13</t>
+          <t xml:space="preserve">v-174</t>
         </is>
       </c>
     </row>
@@ -7283,22 +7498,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7308,17 +7523,17 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">29.03.21</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7348,7 +7563,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-14</t>
+          <t xml:space="preserve">v-175</t>
         </is>
       </c>
     </row>
@@ -7365,22 +7580,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7390,17 +7605,17 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">29.03.21</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7430,7 +7645,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-15</t>
+          <t xml:space="preserve">v-176</t>
         </is>
       </c>
     </row>
@@ -7447,22 +7662,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7472,17 +7687,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">29.03.21</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7512,7 +7727,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-16</t>
+          <t xml:space="preserve">v-177</t>
         </is>
       </c>
     </row>
@@ -7529,22 +7744,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK-Ki #10 P19+10 07.06.21</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7554,17 +7769,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2021-06-07</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">07.06.21</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7594,7 +7809,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-17</t>
+          <t xml:space="preserve">v-178</t>
         </is>
       </c>
     </row>
@@ -7611,22 +7826,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
+          <t xml:space="preserve">HEK-Ki #1 P19+10 07.06.21</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.0</t>
+          <t xml:space="preserve">19+10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7636,17 +7851,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2021-06-07</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.12.19</t>
+          <t xml:space="preserve">07.06.21</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7676,7 +7891,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-18</t>
+          <t xml:space="preserve">v-179</t>
         </is>
       </c>
     </row>
@@ -7693,22 +7908,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
+          <t xml:space="preserve">HEK-Ki #3 P19+10 07.06.21</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.0</t>
+          <t xml:space="preserve">19+10</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7718,17 +7933,17 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2021-06-07</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.12.19</t>
+          <t xml:space="preserve">07.06.21</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7758,7 +7973,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-19</t>
+          <t xml:space="preserve">v-180</t>
         </is>
       </c>
     </row>
@@ -7775,22 +7990,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">HEK-Ki #12 P19+10 07.06.21</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7800,17 +8015,17 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2021-06-07</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">07.06.21</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7840,7 +8055,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-20</t>
+          <t xml:space="preserve">v-181</t>
         </is>
       </c>
     </row>
@@ -7857,22 +8072,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">HEK-Ki #9 P19+10 07.06.21</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7882,17 +8097,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2021-06-07</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">07.06.21</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7922,7 +8137,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-21</t>
+          <t xml:space="preserve">v-182</t>
         </is>
       </c>
     </row>
@@ -7939,22 +8154,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">DuPAR-10CR P106 13.07.21</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">106.0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7964,17 +8179,17 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2021-07-13</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">13.07.21</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8004,7 +8219,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-22</t>
+          <t xml:space="preserve">v-183</t>
         </is>
       </c>
     </row>
@@ -8021,22 +8236,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">DuPAR-10CR P106 13.07.21</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">106.0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8046,17 +8261,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2021-07-13</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">13.07.21</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8086,7 +8301,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-23</t>
+          <t xml:space="preserve">v-184</t>
         </is>
       </c>
     </row>
@@ -8103,17 +8318,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">Panc1 P24 26.12.19</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8128,17 +8343,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2019-12-26</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">26.12.19</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8168,7 +8378,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-24</t>
+          <t xml:space="preserve">v-185</t>
         </is>
       </c>
     </row>
@@ -8185,22 +8395,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
+          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">99.0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8208,14 +8418,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-01-27</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27.01.20</t>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8225,7 +8435,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -8245,7 +8455,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-25</t>
+          <t xml:space="preserve">v-186</t>
         </is>
       </c>
     </row>
@@ -8262,22 +8472,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
+          <t xml:space="preserve">Panc1 P24 26.12.19</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -8285,14 +8495,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-01-27</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27.01.20</t>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8322,7 +8527,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-26</t>
+          <t xml:space="preserve">v-187</t>
         </is>
       </c>
     </row>
@@ -8339,22 +8544,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P80 27.1.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">134.0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8362,14 +8567,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-01-27</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27.01.20</t>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8379,7 +8584,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -8399,7 +8604,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-27</t>
+          <t xml:space="preserve">v-188</t>
         </is>
       </c>
     </row>
@@ -8416,22 +8621,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">99.0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8439,19 +8644,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-12-17</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17.12.20</t>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8461,7 +8661,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8471,7 +8671,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -8481,7 +8681,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-189</t>
         </is>
       </c>
     </row>
@@ -8498,22 +8698,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
+          <t xml:space="preserve">DuDoceR-PARc P84 12.07.21 BARO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">84.0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8521,19 +8721,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-12-17</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17.12.20</t>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8543,7 +8738,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8553,7 +8748,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -8563,7 +8758,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-190</t>
         </is>
       </c>
     </row>
@@ -8580,22 +8775,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
+          <t xml:space="preserve">Du145 P40 29.04.22 BARO</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">40.0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8603,19 +8798,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-12-17</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17.12.20</t>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8635,7 +8825,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -8645,7 +8835,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-191</t>
         </is>
       </c>
     </row>
@@ -8662,22 +8852,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">Du145 P45 04.10.21 BARO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">45.0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8685,19 +8875,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-12-17</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17.12.20</t>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8717,7 +8902,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -8727,7 +8912,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-192</t>
         </is>
       </c>
     </row>
@@ -8744,22 +8929,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">DuPAR-CR 1x15uM recovered P110 19.08.21 BARO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">110.0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8767,19 +8952,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-12-17</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17.12.20</t>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8799,7 +8979,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -8809,7 +8989,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-193</t>
         </is>
       </c>
     </row>
@@ -8826,22 +9006,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-1x15CR P111 19.08.21</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">111.0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8849,19 +9029,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-12-17</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17.12.20</t>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8871,7 +9046,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8881,7 +9056,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -8891,7 +9066,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-194</t>
         </is>
       </c>
     </row>
@@ -8908,22 +9083,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-2x15CR P112 13.09.21</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">112.0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8931,14 +9106,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-09-04</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04.09.20</t>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8948,7 +9123,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8968,7 +9143,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-195</t>
         </is>
       </c>
     </row>
@@ -8985,22 +9160,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">DuPAR-20CR p134 15.04.22</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">134.0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -9008,14 +9183,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-09-04</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04.09.20</t>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9045,7 +9220,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-196</t>
         </is>
       </c>
     </row>
@@ -9062,37 +9237,37 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #11 18.07.21</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-09-04</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9122,7 +9297,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-197</t>
         </is>
       </c>
     </row>
@@ -9139,42 +9314,37 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #31 18.07.21</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-08-06</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06.08.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -9204,7 +9374,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-198</t>
         </is>
       </c>
     </row>
@@ -9221,42 +9391,37 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #32 18.07.21</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-08-06</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06.08.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -9286,7 +9451,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-199</t>
         </is>
       </c>
     </row>
@@ -9303,37 +9468,32 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #20 18.07.21</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-08-01</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -9348,7 +9508,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -9368,7 +9528,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-200</t>
         </is>
       </c>
     </row>
@@ -9385,37 +9545,32 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #25 18.07.21</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-08-01</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -9430,7 +9585,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -9450,7 +9605,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-201</t>
         </is>
       </c>
     </row>
@@ -9467,37 +9622,32 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #24 18.07.21</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-08-01</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -9512,7 +9662,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9532,7 +9682,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-202</t>
         </is>
       </c>
     </row>
@@ -9549,37 +9699,32 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #18 18.07.21</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-08-01</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -9594,7 +9739,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9614,7 +9759,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-203</t>
         </is>
       </c>
     </row>
@@ -9631,37 +9776,32 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #22 18.07.21</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-08-01</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -9676,7 +9816,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9696,7 +9836,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-204</t>
         </is>
       </c>
     </row>
@@ -9713,37 +9853,32 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #13 18.07.21</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-08-01</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -9758,7 +9893,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9778,7 +9913,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-205</t>
         </is>
       </c>
     </row>
@@ -9795,17 +9930,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #3 18.07.21</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9818,14 +9953,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9835,7 +9970,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9855,7 +9990,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-206</t>
         </is>
       </c>
     </row>
@@ -9872,17 +10007,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #5 18.07.21</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9895,14 +10030,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9912,7 +10047,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9932,7 +10067,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-207</t>
         </is>
       </c>
     </row>
@@ -9949,17 +10084,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #8 18.07.21</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -9972,19 +10107,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9994,7 +10124,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -10014,7 +10144,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-208</t>
         </is>
       </c>
     </row>
@@ -10031,17 +10161,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #9 18.07.21</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -10054,19 +10184,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -10076,7 +10201,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -10096,7 +10221,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-209</t>
         </is>
       </c>
     </row>
@@ -10113,17 +10238,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #1 18.07.21</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -10136,19 +10261,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -10178,7 +10298,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-210</t>
         </is>
       </c>
     </row>
@@ -10195,17 +10315,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #26 18.07.21</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -10218,19 +10338,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -10260,7 +10375,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-211</t>
         </is>
       </c>
     </row>
@@ -10277,42 +10392,37 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #29 18.07.21</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">46.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-16</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16.07.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -10342,7 +10452,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-212</t>
         </is>
       </c>
     </row>
@@ -10359,37 +10469,37 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #21 18.07.21</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">79.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-08</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -10419,7 +10529,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-213</t>
         </is>
       </c>
     </row>
@@ -10436,37 +10546,37 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #34 18.07.21</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-08</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -10496,7 +10606,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-214</t>
         </is>
       </c>
     </row>
@@ -10513,37 +10623,37 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #4 18.07.21</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-08</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10573,7 +10683,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-215</t>
         </is>
       </c>
     </row>
@@ -10590,37 +10700,37 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P84 08.07.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #10 18.07.21</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">84.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-08</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10650,7 +10760,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-216</t>
         </is>
       </c>
     </row>
@@ -10667,22 +10777,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22 BARO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">134.0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10690,14 +10800,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-31</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31.07.20</t>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10707,7 +10817,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10727,7 +10837,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-217</t>
         </is>
       </c>
     </row>
@@ -10744,22 +10854,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
+          <t xml:space="preserve">DuPAR-2x20CR P130 25.02.22 BARO</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">130.0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10767,14 +10877,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -10789,7 +10894,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10809,7 +10914,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-218</t>
         </is>
       </c>
     </row>
@@ -10826,22 +10931,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
+          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">39.0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10849,19 +10954,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10871,7 +10966,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10891,7 +10986,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-219</t>
         </is>
       </c>
     </row>
@@ -10908,22 +11003,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">39.0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10931,19 +11026,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10953,7 +11038,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10973,7 +11058,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-220</t>
         </is>
       </c>
     </row>
@@ -10990,22 +11075,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">LNCaP P15-Canada 14.10.21 BARO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">15.0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11013,19 +11098,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -11035,7 +11115,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -11055,7 +11135,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-221</t>
         </is>
       </c>
     </row>
@@ -11072,22 +11152,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">116.0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -11095,14 +11175,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -11117,7 +11192,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -11137,7 +11212,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-222</t>
         </is>
       </c>
     </row>
@@ -11154,22 +11229,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">116.0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -11177,14 +11252,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-20</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.07.20</t>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -11199,7 +11269,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11219,7 +11289,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-223</t>
         </is>
       </c>
     </row>
@@ -11236,22 +11306,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">116.0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -11259,14 +11329,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-14</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14.07.20</t>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -11276,7 +11346,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -11296,7 +11366,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-224</t>
         </is>
       </c>
     </row>
@@ -11313,22 +11383,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">DuDoceR-1x25CR P122 30.03.22 BARO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">122.0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -11336,14 +11406,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-14</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14.07.20</t>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -11353,7 +11423,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -11373,7 +11443,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-225</t>
         </is>
       </c>
     </row>
@@ -11390,22 +11460,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">116.0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -11413,14 +11483,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-10</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.07.20</t>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -11430,7 +11500,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -11450,7 +11520,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-226</t>
         </is>
       </c>
     </row>
@@ -11467,37 +11537,37 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
+          <t xml:space="preserve">HepG2 PX+11 02.10.21 BARO</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.0</t>
+          <t xml:space="preserve">X+11</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-10</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -11527,7 +11597,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-227</t>
         </is>
       </c>
     </row>
@@ -11544,22 +11614,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P85 10.07.20 BARO</t>
+          <t xml:space="preserve">Huh7 P32 23.10.21 BARO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">85.0</t>
+          <t xml:space="preserve">32.0</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -11567,14 +11637,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-10</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.07.20</t>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -11604,7 +11674,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-228</t>
         </is>
       </c>
     </row>
@@ -11621,22 +11691,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO</t>
+          <t xml:space="preserve">DuPAR-15CR* P122 16.12.21 BARO</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.0</t>
+          <t xml:space="preserve">122.0</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11644,19 +11714,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-02-17</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17.02.20</t>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11686,7 +11751,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-229</t>
         </is>
       </c>
     </row>
@@ -11703,42 +11768,37 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC)</t>
+          <t xml:space="preserve">DuPAR-luc 30.03.22 Ayça</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-02-17</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17.02.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11768,7 +11828,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-230</t>
         </is>
       </c>
     </row>
@@ -11785,37 +11845,37 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
+          <t xml:space="preserve">Huh7 P32 23.10.21 BARO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">32.0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-03-13</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13.03.20</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11825,7 +11885,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11845,7 +11905,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-231</t>
         </is>
       </c>
     </row>
@@ -11862,17 +11922,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
+          <t xml:space="preserve">DtxR-luc 30.03.22 Ayça</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -11885,14 +11945,9 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-03-13</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13.03.20</t>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11902,7 +11957,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11922,7 +11977,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-232</t>
         </is>
       </c>
     </row>
@@ -11939,22 +11994,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">116.0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11962,14 +12017,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-14</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14.07.20</t>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11979,7 +12034,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11999,7 +12054,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-233</t>
         </is>
       </c>
     </row>
@@ -12016,37 +12071,32 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">PC3 cell pellet</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-14</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -12076,7 +12126,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-234</t>
         </is>
       </c>
     </row>
@@ -12093,37 +12143,32 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
+          <t xml:space="preserve">PC3 cell pellet</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-10</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -12153,7 +12198,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-235</t>
         </is>
       </c>
     </row>
@@ -12170,37 +12215,37 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
+          <t xml:space="preserve">LNCaP pellet</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-07-10</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -12230,7 +12275,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-236</t>
         </is>
       </c>
     </row>
@@ -12247,42 +12292,37 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">LNCaP pellet</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-03-02</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -12312,7 +12352,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-237</t>
         </is>
       </c>
     </row>
@@ -12329,42 +12369,32 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">U2OS pellet</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-03-02</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -12394,7 +12424,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-238</t>
         </is>
       </c>
     </row>
@@ -12411,42 +12441,37 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">Huh7 pellet</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-03-02</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -12476,7 +12501,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-239</t>
         </is>
       </c>
     </row>
@@ -12493,42 +12518,32 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">U373 pellet</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-03-02</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -12558,7 +12573,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-240</t>
         </is>
       </c>
     </row>
@@ -12575,42 +12590,37 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">HepG2 pellet</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-03-02</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -12640,7 +12650,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-241</t>
         </is>
       </c>
     </row>
@@ -12657,42 +12667,32 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">MDA-231 pellet</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-03-02</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-242</t>
         </is>
       </c>
     </row>
@@ -57034,7 +57034,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -57052,26 +57052,26 @@
         <v>81</v>
       </c>
       <c r="I8">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -57089,10 +57089,10 @@
         <v>81</v>
       </c>
       <c r="I9">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -57108,7 +57108,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -57126,10 +57126,10 @@
         <v>81</v>
       </c>
       <c r="I10">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="J10">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -161,7 +161,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -171,12 +171,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -186,17 +186,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -226,7 +226,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-2</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -243,7 +243,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -253,12 +253,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -268,17 +268,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -298,7 +298,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -308,7 +308,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-3</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -325,7 +325,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -335,12 +335,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -350,17 +350,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -380,7 +380,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -390,7 +390,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-4</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -407,7 +407,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -417,12 +417,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -432,17 +432,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-5</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -514,17 +514,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-6</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-7</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -678,17 +678,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-09-04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -718,7 +713,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-8</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -735,7 +730,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -745,12 +740,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -760,17 +755,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-09-04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -800,7 +790,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-9</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -817,7 +807,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -827,12 +817,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -842,17 +832,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-09-04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -882,7 +867,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-10</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -899,7 +884,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -909,12 +894,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -924,12 +909,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-08-06</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">06.08.20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -964,7 +949,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-11</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -981,7 +966,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -991,12 +976,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1006,12 +991,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-08-06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">06.08.20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1046,7 +1031,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-12</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1048,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1073,12 +1058,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1088,17 +1073,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1108,7 +1093,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1128,7 +1113,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-13</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1130,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1155,12 +1140,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1170,17 +1155,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1190,7 +1175,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1210,7 +1195,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-14</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1212,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1237,12 +1222,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,17 +1237,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1272,7 +1257,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1292,7 +1277,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-15</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1294,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1319,12 +1304,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1334,17 +1319,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1354,7 +1339,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1374,7 +1359,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-16</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1376,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1401,12 +1386,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1416,17 +1401,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1436,7 +1421,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1456,7 +1441,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-17</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1458,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1483,12 +1468,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1498,17 +1483,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.12.19</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1518,7 +1503,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1538,7 +1523,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-18</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1540,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1565,32 +1550,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.12.19</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1600,7 +1580,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1620,7 +1600,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-19</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1617,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1647,32 +1627,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1682,7 +1657,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1702,7 +1677,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-20</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1694,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1729,32 +1704,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1764,7 +1739,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1784,7 +1759,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-21</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1776,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1811,32 +1786,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1846,7 +1821,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1866,7 +1841,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-22</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1858,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1893,32 +1868,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1948,7 +1923,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-23</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1940,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1975,32 +1950,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2030,7 +2005,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-24</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2022,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2057,12 +2032,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
+          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">46.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2072,12 +2047,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve">2020-07-16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.01.20</t>
+          <t xml:space="preserve">16.07.20</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2107,7 +2087,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-25</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2104,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2134,12 +2114,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">79.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2149,12 +2129,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.01.20</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2184,7 +2164,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-26</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2181,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2211,12 +2191,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P80 27.1.20 BARO</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2226,12 +2206,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.01.20</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2261,7 +2241,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-27</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -2283,17 +2263,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2303,17 +2283,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2333,7 +2308,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2343,7 +2318,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -2365,17 +2340,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
+          <t xml:space="preserve">U373 P84 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">84.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2385,17 +2360,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2415,7 +2385,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2425,7 +2395,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -2447,17 +2417,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
+          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2467,17 +2437,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">31.07.20</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2497,7 +2462,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2507,7 +2472,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -2529,17 +2494,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">52.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2549,17 +2514,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2569,7 +2534,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2579,7 +2544,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2589,7 +2554,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -2611,17 +2576,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">52.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2631,17 +2596,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2651,7 +2616,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2661,7 +2626,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2671,7 +2636,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -2693,17 +2658,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2713,17 +2678,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2733,7 +2698,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2743,7 +2708,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2753,7 +2718,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -2775,17 +2740,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2795,12 +2760,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-04</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2810,7 +2780,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2830,7 +2800,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -2852,17 +2822,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2872,12 +2842,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-04</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2907,7 +2882,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -2929,17 +2904,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2949,12 +2924,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-04</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2984,7 +2964,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -3006,17 +2986,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3026,17 +3006,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-06</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">06.08.20</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3066,7 +3041,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -3088,17 +3063,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3108,17 +3083,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-06</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">06.08.20</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3148,7 +3118,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -3170,17 +3140,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3190,17 +3160,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3210,7 +3175,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3230,7 +3195,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -3252,17 +3217,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">77.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3272,17 +3237,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3292,7 +3252,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3312,7 +3272,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -3334,17 +3294,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">U373 P85 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">85.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3354,17 +3314,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3374,7 +3329,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3394,7 +3349,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -3416,17 +3371,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">29.0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3436,17 +3391,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3456,7 +3411,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3476,7 +3431,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -3498,17 +3453,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">36.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3518,17 +3473,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3538,7 +3493,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3558,7 +3513,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -3580,37 +3535,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-03-13</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3620,7 +3570,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3640,7 +3590,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3612,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3682,12 +3632,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-03-13</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3717,7 +3667,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -3739,32 +3689,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3774,7 +3724,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3794,7 +3744,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -3816,37 +3766,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3856,7 +3801,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3876,7 +3821,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -3898,37 +3843,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3938,7 +3878,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3958,7 +3898,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -3980,37 +3920,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">77.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4040,7 +3975,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -4062,37 +3997,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4122,7 +4057,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -4144,17 +4079,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">46.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4164,17 +4099,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-16</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4204,7 +4139,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4161,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">79.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4246,12 +4181,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4281,7 +4221,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -4303,17 +4243,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4323,12 +4263,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4358,7 +4303,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -4380,17 +4325,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4400,12 +4345,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4435,7 +4385,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -4457,17 +4407,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P84 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">84.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4477,12 +4427,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4512,7 +4467,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -4524,27 +4479,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4554,12 +4509,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-31</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.07.20</t>
+          <t xml:space="preserve">10.02.20</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4589,7 +4549,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-2</t>
         </is>
       </c>
     </row>
@@ -4601,27 +4561,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4631,17 +4591,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4651,7 +4611,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4671,7 +4631,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-3</t>
         </is>
       </c>
     </row>
@@ -4683,27 +4643,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4713,17 +4673,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4733,7 +4693,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4753,7 +4713,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-4</t>
         </is>
       </c>
     </row>
@@ -4765,27 +4725,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4795,17 +4755,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4815,7 +4775,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4835,7 +4795,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-5</t>
         </is>
       </c>
     </row>
@@ -4847,27 +4807,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4877,17 +4837,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4897,7 +4857,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4917,7 +4877,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-6</t>
         </is>
       </c>
     </row>
@@ -4929,27 +4889,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4959,17 +4919,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4999,7 +4959,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-7</t>
         </is>
       </c>
     </row>
@@ -5011,27 +4971,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5041,17 +5001,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5081,7 +5041,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-8</t>
         </is>
       </c>
     </row>
@@ -5093,27 +5053,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5123,12 +5083,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">15.12.19</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5158,7 +5123,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-9</t>
         </is>
       </c>
     </row>
@@ -5170,27 +5135,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5200,12 +5165,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">14.12.19</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5235,7 +5205,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-10</t>
         </is>
       </c>
     </row>
@@ -5247,27 +5217,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5277,12 +5247,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">14.12.19</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5312,7 +5287,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-11</t>
         </is>
       </c>
     </row>
@@ -5324,27 +5299,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5354,12 +5329,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">14.12.19</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5389,7 +5369,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-12</t>
         </is>
       </c>
     </row>
@@ -5401,27 +5381,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P85 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">85.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5431,12 +5411,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">14.12.19</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5466,7 +5451,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-13</t>
         </is>
       </c>
     </row>
@@ -5478,27 +5463,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5508,12 +5493,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-17</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.20</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5548,7 +5533,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-14</t>
         </is>
       </c>
     </row>
@@ -5560,27 +5545,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC)</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5590,12 +5575,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-17</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5630,7 +5615,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-15</t>
         </is>
       </c>
     </row>
@@ -5642,42 +5627,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-13</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.20</t>
+          <t xml:space="preserve">10.02.20</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5687,7 +5677,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5707,7 +5697,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-16</t>
         </is>
       </c>
     </row>
@@ -5719,42 +5709,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-13</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.20</t>
+          <t xml:space="preserve">10.02.20</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5764,7 +5759,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5784,7 +5779,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-17</t>
         </is>
       </c>
     </row>
@@ -5796,27 +5791,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">25.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5826,12 +5821,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">22.12.19</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-18</t>
         </is>
       </c>
     </row>
@@ -5873,27 +5873,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">25.0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5903,12 +5903,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">22.12.19</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5938,7 +5943,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-19</t>
         </is>
       </c>
     </row>
@@ -5950,27 +5955,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5980,12 +5985,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">01.01.20</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6015,7 +6025,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-20</t>
         </is>
       </c>
     </row>
@@ -6027,27 +6037,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6057,12 +6067,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">01.01.20</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6092,7 +6107,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-21</t>
         </is>
       </c>
     </row>
@@ -6104,27 +6119,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6134,17 +6149,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6174,7 +6189,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-22</t>
         </is>
       </c>
     </row>
@@ -6186,27 +6201,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6216,17 +6231,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6256,7 +6271,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-23</t>
         </is>
       </c>
     </row>
@@ -6268,27 +6283,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6298,17 +6313,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6338,7 +6353,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-24</t>
         </is>
       </c>
     </row>
@@ -6350,27 +6365,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6380,17 +6395,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-27</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6420,7 +6430,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-25</t>
         </is>
       </c>
     </row>
@@ -6432,27 +6442,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6462,17 +6472,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-27</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6502,7 +6507,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-26</t>
         </is>
       </c>
     </row>
@@ -6514,27 +6519,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">U373 P80 27.1.20 BARO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6544,17 +6549,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-01-27</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-27</t>
         </is>
       </c>
     </row>
@@ -57034,7 +57034,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -57052,10 +57052,10 @@
         <v>81</v>
       </c>
       <c r="I8">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J8">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -57066,12 +57066,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -57089,10 +57089,10 @@
         <v>81</v>
       </c>
       <c r="I9">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J9">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -156,12 +156,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -171,12 +171,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -186,17 +186,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -226,7 +226,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-2</t>
         </is>
       </c>
     </row>
@@ -238,12 +238,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -253,12 +253,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -268,17 +268,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -298,7 +298,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -308,7 +308,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-3</t>
         </is>
       </c>
     </row>
@@ -320,12 +320,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -335,12 +335,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -350,17 +350,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -380,7 +380,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -390,7 +390,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-4</t>
         </is>
       </c>
     </row>
@@ -402,12 +402,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -417,12 +417,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -432,17 +432,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-5</t>
         </is>
       </c>
     </row>
@@ -484,12 +484,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -514,17 +514,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-6</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">19+7</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.12.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-7</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -678,12 +678,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-04</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">15.12.19</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -713,7 +718,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-8</t>
         </is>
       </c>
     </row>
@@ -725,12 +730,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -740,12 +745,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -755,12 +760,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-04</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">15.12.19</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -790,7 +800,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-9</t>
         </is>
       </c>
     </row>
@@ -802,12 +812,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -817,12 +827,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -832,12 +842,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-04</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.09.20</t>
+          <t xml:space="preserve">14.12.19</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -867,7 +882,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-10</t>
         </is>
       </c>
     </row>
@@ -879,12 +894,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -894,12 +909,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -909,12 +924,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-06</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">06.08.20</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -949,7 +964,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-11</t>
         </is>
       </c>
     </row>
@@ -961,12 +976,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -976,12 +991,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -991,12 +1006,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-06</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">06.08.20</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1031,7 +1046,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-12</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1058,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1058,12 +1073,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1073,17 +1088,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1093,7 +1108,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1113,7 +1128,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-13</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1140,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1140,12 +1155,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1155,17 +1170,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2019-12-14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1175,7 +1190,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1195,7 +1210,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-14</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1222,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1222,12 +1237,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1237,17 +1252,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2019-12-15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1257,7 +1272,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1277,7 +1292,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-15</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1304,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1304,12 +1319,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1319,17 +1334,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1339,7 +1354,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1359,7 +1374,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-16</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1386,12 +1401,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1401,17 +1416,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1421,7 +1436,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1441,7 +1456,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-17</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1468,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1468,12 +1483,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">25.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1483,17 +1498,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-01</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.20</t>
+          <t xml:space="preserve">22.12.19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1503,7 +1518,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1523,7 +1538,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-18</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1550,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1550,27 +1565,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">25.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">22.12.19</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1580,7 +1600,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1600,7 +1620,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-19</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1632,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1627,27 +1647,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">01.01.20</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1657,7 +1682,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1677,7 +1702,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-20</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1714,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1704,32 +1729,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1739,7 +1764,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1759,7 +1784,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-21</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1796,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1786,32 +1811,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1821,7 +1846,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1841,7 +1866,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-22</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1878,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1868,32 +1893,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1923,7 +1948,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-23</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1960,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1950,32 +1975,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-01-01</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2005,7 +2030,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-24</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2042,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2032,12 +2057,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">46.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2047,17 +2072,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-16</t>
+          <t xml:space="preserve">2020-01-27</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.07.20</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2087,7 +2107,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-25</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2119,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2114,12 +2134,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">79.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2129,12 +2149,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-01-27</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2164,7 +2184,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-26</t>
         </is>
       </c>
     </row>
@@ -2176,12 +2196,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2191,12 +2211,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
+          <t xml:space="preserve">U373 P80 27.1.20 BARO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2206,12 +2226,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-01-27</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2241,7 +2261,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-27</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2273,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2263,17 +2283,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2283,12 +2303,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">17.12.20</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2308,7 +2333,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2318,7 +2343,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2355,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2340,17 +2365,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P84 08.07.20 BARO</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">84.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2360,12 +2385,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">08.07.20</t>
+          <t xml:space="preserve">17.12.20</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2385,7 +2415,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2395,7 +2425,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2437,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2417,17 +2447,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2437,12 +2467,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-31</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.07.20</t>
+          <t xml:space="preserve">17.12.20</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2462,7 +2497,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2472,7 +2507,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2519,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2494,17 +2529,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2514,17 +2549,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2534,7 +2569,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2544,7 +2579,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2554,7 +2589,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2601,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2576,17 +2611,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2596,17 +2631,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2616,7 +2651,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2626,7 +2661,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2636,7 +2671,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2683,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2658,17 +2693,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">19+7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2678,17 +2713,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
+          <t xml:space="preserve">17.12.20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2698,7 +2733,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2708,7 +2743,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2718,7 +2753,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2765,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2740,17 +2775,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2760,17 +2795,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-09-04</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2780,7 +2810,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2800,7 +2830,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2842,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2822,17 +2852,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2842,17 +2872,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-09-04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2882,7 +2907,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2919,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2904,17 +2929,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">51.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2924,17 +2949,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-20</t>
+          <t xml:space="preserve">2020-09-04</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.07.20</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2964,7 +2984,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2996,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2986,17 +3006,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3006,12 +3026,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2020-08-06</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">06.08.20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3041,7 +3066,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3078,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3063,17 +3088,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3083,12 +3108,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2020-08-06</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">06.08.20</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3118,7 +3148,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3160,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3140,17 +3170,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3160,12 +3190,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">01.08.20</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3175,7 +3210,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3195,7 +3230,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3242,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3217,17 +3252,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3237,12 +3272,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">01.08.20</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3252,7 +3292,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3272,7 +3312,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3324,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3294,17 +3334,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P85 10.07.20 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">85.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3314,12 +3354,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">01.08.20</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3329,7 +3374,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3349,7 +3394,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3406,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3371,17 +3416,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3391,17 +3436,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-17</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.20</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3411,7 +3456,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3431,7 +3476,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3488,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3453,17 +3498,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC)</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3473,17 +3518,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-17</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.20</t>
+          <t xml:space="preserve">01.08.20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3493,7 +3538,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3513,7 +3558,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3570,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3535,32 +3580,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-13</t>
+          <t xml:space="preserve">2020-08-01</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.20</t>
+          <t xml:space="preserve">01.08.20</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3570,7 +3620,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">CabaR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3590,7 +3640,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3652,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3612,12 +3662,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3632,12 +3682,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-13</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3667,7 +3717,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3729,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3689,32 +3739,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3724,7 +3774,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3744,7 +3794,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3806,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3766,32 +3816,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.07.20</t>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3801,7 +3856,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3821,7 +3876,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3888,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3843,32 +3898,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3878,7 +3938,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3898,7 +3958,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3970,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3920,32 +3980,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-10</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.07.20</t>
+          <t xml:space="preserve">20.07.20</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3975,7 +4040,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -3987,7 +4052,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3997,37 +4062,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4057,7 +4122,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4134,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4079,17 +4144,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">46.0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4099,17 +4164,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-07-16</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
+          <t xml:space="preserve">16.07.20</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HeLa</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4139,7 +4204,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4216,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4161,17 +4226,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">79.0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4181,17 +4246,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4221,7 +4281,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4293,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4243,17 +4303,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4263,17 +4323,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4303,7 +4358,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4370,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4325,17 +4380,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">76.0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4345,17 +4400,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4385,7 +4435,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4447,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4407,17 +4457,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
+          <t xml:space="preserve">U373 P84 08.07.20 BARO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">84.0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4427,17 +4477,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-02</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4467,7 +4512,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -4484,22 +4529,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4509,17 +4554,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-07-31</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">31.07.20</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4549,7 +4589,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-2</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -4566,22 +4606,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">52.0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4591,17 +4631,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4611,7 +4651,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4631,7 +4671,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-3</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -4648,22 +4688,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">52.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4673,17 +4713,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4693,7 +4733,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4713,7 +4753,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-4</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -4730,22 +4770,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4755,17 +4795,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4775,7 +4815,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4795,7 +4835,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-5</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -4812,22 +4852,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4837,17 +4877,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4857,7 +4897,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4877,7 +4917,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-6</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -4894,22 +4934,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4919,17 +4959,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4959,7 +4999,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-7</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -4976,22 +5016,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">51.0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5001,17 +5041,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-07-20</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5041,7 +5081,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-8</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -5058,22 +5098,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5083,17 +5123,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5123,7 +5158,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-9</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -5140,22 +5175,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5165,17 +5200,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5205,7 +5235,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-10</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -5222,22 +5252,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5247,17 +5277,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5287,7 +5312,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-11</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -5304,22 +5329,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">77.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5329,17 +5354,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5369,7 +5389,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-12</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -5386,22 +5406,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">U373 P85 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">85.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5411,17 +5431,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5451,7 +5466,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-13</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -5468,22 +5483,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO</t>
+          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">29.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5493,12 +5508,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-14</t>
+          <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.12.19</t>
+          <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5533,7 +5548,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-14</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -5550,22 +5565,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO</t>
+          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">36.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5575,12 +5590,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-15</t>
+          <t xml:space="preserve">2020-02-17</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.12.19</t>
+          <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5615,7 +5630,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-15</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -5632,42 +5647,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-03-13</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5677,7 +5687,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5697,7 +5707,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-16</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -5714,42 +5724,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-03-13</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5759,7 +5764,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5779,7 +5784,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-17</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -5796,22 +5801,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5821,17 +5826,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.12.19</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-18</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -5878,22 +5878,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5903,17 +5903,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.12.19</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5943,7 +5938,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-19</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -5960,22 +5955,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">80.0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5985,17 +5980,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6025,7 +6015,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-20</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -6042,22 +6032,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">77.0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6067,17 +6057,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-07-10</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6107,7 +6092,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-21</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -6124,22 +6109,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6149,17 +6134,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6189,7 +6174,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-22</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -6206,22 +6191,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6231,17 +6216,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6271,7 +6256,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-23</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -6288,22 +6273,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6313,17 +6298,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-01</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.01.20</t>
+          <t xml:space="preserve">02.03.20</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6353,7 +6338,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-24</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -6370,22 +6355,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6395,12 +6380,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.01.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6430,7 +6420,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-25</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -6447,22 +6437,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6472,12 +6462,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.01.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6507,7 +6502,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-26</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -6524,22 +6519,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P80 27.1.20 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">80.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6549,12 +6544,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve">2020-03-02</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.01.20</t>
+          <t xml:space="preserve">02.03.20</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-27</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -57029,12 +57029,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -57052,10 +57052,10 @@
         <v>81</v>
       </c>
       <c r="I8">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J8">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -57071,7 +57071,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -57089,10 +57089,10 @@
         <v>81</v>
       </c>
       <c r="I9">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -6591,12 +6591,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6673,12 +6673,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6755,12 +6755,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6832,12 +6832,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6914,12 +6914,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6996,12 +6996,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7078,12 +7078,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7160,12 +7160,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7242,12 +7242,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7324,12 +7324,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7406,12 +7406,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7488,12 +7488,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7570,12 +7570,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7652,12 +7652,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7734,12 +7734,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7816,12 +7816,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7898,12 +7898,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7980,12 +7980,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8062,12 +8062,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8144,12 +8144,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8226,12 +8226,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -8308,12 +8308,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8385,12 +8385,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8462,12 +8462,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8534,12 +8534,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8611,12 +8611,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8688,12 +8688,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -8765,12 +8765,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8842,12 +8842,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8919,12 +8919,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8996,12 +8996,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9073,12 +9073,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -9150,12 +9150,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9227,12 +9227,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9304,12 +9304,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9381,12 +9381,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -9458,12 +9458,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -9535,12 +9535,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9612,12 +9612,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9689,12 +9689,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9766,12 +9766,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -9843,12 +9843,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9920,12 +9920,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9997,12 +9997,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -10074,12 +10074,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -10151,12 +10151,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -10228,12 +10228,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -10305,12 +10305,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -10382,12 +10382,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -10459,12 +10459,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10536,12 +10536,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10613,12 +10613,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10690,12 +10690,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10767,12 +10767,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10844,12 +10844,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10921,12 +10921,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -10993,12 +10993,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -11065,12 +11065,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -11142,12 +11142,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -11219,12 +11219,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -11296,12 +11296,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11373,12 +11373,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -11450,12 +11450,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -11527,12 +11527,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -11604,12 +11604,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -11681,12 +11681,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -11758,12 +11758,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11835,12 +11835,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11912,12 +11912,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11984,12 +11984,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -12061,12 +12061,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -12133,12 +12133,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -12205,12 +12205,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -12282,12 +12282,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -12359,12 +12359,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -12431,12 +12431,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -12508,12 +12508,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -12580,12 +12580,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -12657,12 +12657,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -57098,12 +57098,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -12729,12 +12729,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -12806,12 +12806,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -12883,12 +12883,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -12960,12 +12960,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -13037,12 +13037,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -13114,12 +13114,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -13191,12 +13191,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -13268,12 +13268,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -13345,12 +13345,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -13422,12 +13422,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -13499,12 +13499,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -13576,12 +13576,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -13653,12 +13653,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -13730,12 +13730,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -13807,12 +13807,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -13884,12 +13884,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -13961,12 +13961,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -14038,12 +14038,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -14115,12 +14115,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -14187,12 +14187,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -14264,12 +14264,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -14336,12 +14336,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -14408,12 +14408,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -14480,12 +14480,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -14557,12 +14557,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -14629,12 +14629,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -14701,12 +14701,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -14773,12 +14773,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -14850,12 +14850,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -14927,12 +14927,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -15004,12 +15004,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -15081,12 +15081,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -15158,12 +15158,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -15235,12 +15235,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -15312,12 +15312,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -15389,12 +15389,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -15461,12 +15461,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -15533,12 +15533,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -15610,12 +15610,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -15687,12 +15687,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -15759,12 +15759,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -15836,12 +15836,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -15913,12 +15913,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -15990,12 +15990,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -16062,12 +16062,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -16139,12 +16139,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -16211,12 +16211,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -16283,12 +16283,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -16360,12 +16360,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -16432,12 +16432,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -16509,12 +16509,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -16586,12 +16586,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -16663,12 +16663,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -16740,12 +16740,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -16817,12 +16817,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -16894,12 +16894,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -16971,12 +16971,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -17048,12 +17048,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -17125,12 +17125,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -17202,12 +17202,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -17279,12 +17279,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -17351,12 +17351,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -17428,12 +17428,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -17505,12 +17505,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -17582,12 +17582,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -17659,12 +17659,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -17731,12 +17731,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -17808,12 +17808,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -17885,12 +17885,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -17962,12 +17962,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -18039,12 +18039,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -18116,12 +18116,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -18193,12 +18193,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -57135,12 +57135,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -18270,12 +18270,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -18347,12 +18347,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -18424,12 +18424,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -18501,12 +18501,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -18578,12 +18578,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -18655,12 +18655,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -18732,12 +18732,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -18809,12 +18809,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -18886,12 +18886,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -18963,12 +18963,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -19040,12 +19040,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -19117,12 +19117,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -19194,12 +19194,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -19271,12 +19271,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -19348,12 +19348,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -19425,12 +19425,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -19502,12 +19502,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -19579,12 +19579,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -19656,12 +19656,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -19733,12 +19733,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -19810,12 +19810,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -19887,12 +19887,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -19964,12 +19964,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -20041,12 +20041,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -20118,12 +20118,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -20195,12 +20195,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -20272,12 +20272,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -20344,12 +20344,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -20416,12 +20416,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -20488,12 +20488,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -20560,12 +20560,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -20632,12 +20632,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -20704,12 +20704,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -20776,12 +20776,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -20848,12 +20848,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -20920,12 +20920,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -20992,12 +20992,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -21064,12 +21064,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -21136,12 +21136,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -21208,12 +21208,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -21280,12 +21280,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -21352,12 +21352,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -21424,12 +21424,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -21496,12 +21496,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -21568,12 +21568,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -21640,12 +21640,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -21712,12 +21712,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -21784,12 +21784,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -21856,12 +21856,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -21928,12 +21928,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -22000,12 +22000,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -22072,12 +22072,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -22144,12 +22144,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -22216,12 +22216,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -22288,12 +22288,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -22360,12 +22360,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -22432,12 +22432,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -22504,12 +22504,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -22576,12 +22576,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -22643,12 +22643,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -22715,12 +22715,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -22787,12 +22787,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -22859,12 +22859,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -22931,12 +22931,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -23003,12 +23003,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -23075,12 +23075,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -23147,12 +23147,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -23219,12 +23219,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -23291,12 +23291,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -57172,12 +57172,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -23363,12 +23363,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -23430,12 +23430,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -23497,12 +23497,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -23569,12 +23569,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -23641,12 +23641,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -23713,12 +23713,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -23785,12 +23785,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -23857,12 +23857,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -23929,12 +23929,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -24001,12 +24001,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -24073,12 +24073,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -24145,12 +24145,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -24217,12 +24217,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -24289,12 +24289,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -24361,12 +24361,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -24433,12 +24433,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -24500,12 +24500,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -24572,12 +24572,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -24644,12 +24644,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -24716,12 +24716,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -24788,12 +24788,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -24860,12 +24860,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -24932,12 +24932,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -25004,12 +25004,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -25076,12 +25076,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -25148,12 +25148,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -25220,12 +25220,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -25292,12 +25292,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -25359,12 +25359,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -25431,12 +25431,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -25503,12 +25503,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -25575,12 +25575,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -25642,12 +25642,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -25714,12 +25714,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -25786,12 +25786,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -25858,12 +25858,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -25925,12 +25925,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -25992,12 +25992,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -26064,12 +26064,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -26136,12 +26136,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -26208,12 +26208,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -26280,12 +26280,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -26352,12 +26352,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -26424,12 +26424,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -26496,12 +26496,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -26568,12 +26568,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -26640,12 +26640,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -26712,12 +26712,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -26779,12 +26779,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -26846,12 +26846,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -26918,12 +26918,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -26990,12 +26990,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -27057,12 +27057,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -27129,12 +27129,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -27196,12 +27196,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -27268,12 +27268,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -27340,12 +27340,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -27412,12 +27412,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -27479,12 +27479,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -27551,12 +27551,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -27623,12 +27623,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -27690,12 +27690,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -27762,12 +27762,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -27834,12 +27834,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -27906,12 +27906,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -27978,12 +27978,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -28050,12 +28050,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -28117,12 +28117,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -28189,12 +28189,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -28261,12 +28261,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -28333,12 +28333,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -28400,12 +28400,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -28472,12 +28472,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -28544,12 +28544,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -28616,12 +28616,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -28688,12 +28688,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -57209,12 +57209,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57246,17 +57246,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,10 +57274,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>18</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -57293,7 +57293,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2</t>
+          <t xml:space="preserve">LiqNitro 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">LiqNitro 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,10 +57348,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J16">
-        <v>81</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -57367,7 +57367,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57404,7 +57404,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -28760,12 +28760,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -28832,12 +28832,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -28904,12 +28904,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -28976,12 +28976,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -29048,12 +29048,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -29120,12 +29120,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -29192,12 +29192,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -29264,12 +29264,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -29336,12 +29336,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -29408,12 +29408,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -29480,12 +29480,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -29552,12 +29552,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -29624,12 +29624,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -29696,12 +29696,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -29768,12 +29768,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -29840,12 +29840,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -29912,12 +29912,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -29984,12 +29984,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -30056,12 +30056,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -30128,12 +30128,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -30200,12 +30200,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -30272,12 +30272,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -30344,12 +30344,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -30416,12 +30416,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -30488,12 +30488,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -30560,12 +30560,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -30632,12 +30632,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -30704,12 +30704,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -30776,12 +30776,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -30848,12 +30848,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -30920,12 +30920,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -30992,12 +30992,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -31064,12 +31064,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -31136,12 +31136,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -31208,12 +31208,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -31280,12 +31280,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -31352,12 +31352,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -31424,12 +31424,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -31496,12 +31496,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -31568,12 +31568,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -31640,12 +31640,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -31712,12 +31712,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -31784,12 +31784,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -31856,12 +31856,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -31923,12 +31923,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -31995,12 +31995,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -32067,12 +32067,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -32139,12 +32139,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -32211,12 +32211,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -32283,12 +32283,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -32355,12 +32355,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -32427,12 +32427,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -32499,12 +32499,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -32566,12 +32566,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -32633,12 +32633,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -32705,12 +32705,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -32777,12 +32777,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -32849,12 +32849,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -32921,12 +32921,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -32993,12 +32993,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -33065,12 +33065,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -33137,12 +33137,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -33204,12 +33204,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -57024,17 +57024,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">LiqNitro 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -57052,10 +57052,10 @@
         <v>81</v>
       </c>
       <c r="I8">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="J8">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -57071,7 +57071,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -57089,10 +57089,10 @@
         <v>81</v>
       </c>
       <c r="I9">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J9">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -57108,7 +57108,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -57126,10 +57126,10 @@
         <v>81</v>
       </c>
       <c r="I10">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -57145,7 +57145,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -57163,10 +57163,10 @@
         <v>81</v>
       </c>
       <c r="I11">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -57182,7 +57182,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -57200,10 +57200,10 @@
         <v>81</v>
       </c>
       <c r="I12">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J12">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -57219,7 +57219,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,10 +57237,10 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -57251,12 +57251,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,26 +57274,26 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J14">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>18</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -33271,12 +33271,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -33343,12 +33343,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -33415,12 +33415,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -33487,12 +33487,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -33559,12 +33559,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -33631,12 +33631,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -33703,12 +33703,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -33775,12 +33775,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -33847,12 +33847,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -33919,12 +33919,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -33991,12 +33991,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -34063,12 +34063,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -34135,12 +34135,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -34207,12 +34207,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -34279,12 +34279,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -34351,12 +34351,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -34423,12 +34423,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -34495,12 +34495,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -34567,12 +34567,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -34639,12 +34639,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -34711,12 +34711,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -34783,12 +34783,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -34855,12 +34855,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -34927,12 +34927,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -34999,12 +34999,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -35071,12 +35071,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -35143,12 +35143,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -35215,12 +35215,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -35287,12 +35287,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -35359,12 +35359,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -35431,12 +35431,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -35503,12 +35503,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -35575,12 +35575,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -35647,12 +35647,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -35719,12 +35719,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -35791,12 +35791,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -35863,12 +35863,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -35935,12 +35935,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -36007,12 +36007,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -36079,12 +36079,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -36151,12 +36151,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -36223,12 +36223,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -36295,12 +36295,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -36367,12 +36367,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -36439,12 +36439,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -36511,12 +36511,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -36583,12 +36583,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -36655,12 +36655,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -36727,12 +36727,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -36799,12 +36799,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -36871,12 +36871,12 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -36943,12 +36943,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -37015,12 +37015,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -37087,12 +37087,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -37159,12 +37159,12 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -37231,12 +37231,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -37303,12 +37303,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -37375,12 +37375,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -37447,12 +37447,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -37519,12 +37519,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -37591,12 +37591,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -37663,12 +37663,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -37745,12 +37745,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -37822,12 +37822,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -37899,12 +37899,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -37981,12 +37981,12 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -38063,12 +38063,12 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -38145,12 +38145,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -38227,12 +38227,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -38309,12 +38309,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -38391,12 +38391,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -38473,12 +38473,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -38555,12 +38555,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -38637,12 +38637,12 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -38719,12 +38719,12 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -57061,17 +57061,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">LiqNitro 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -57089,10 +57089,10 @@
         <v>81</v>
       </c>
       <c r="I9">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -57108,7 +57108,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -57126,10 +57126,10 @@
         <v>81</v>
       </c>
       <c r="I10">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J10">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -57145,7 +57145,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -57163,10 +57163,10 @@
         <v>81</v>
       </c>
       <c r="I11">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -57182,7 +57182,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -57200,10 +57200,10 @@
         <v>81</v>
       </c>
       <c r="I12">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J12">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -57219,7 +57219,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,10 +57237,10 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J13">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -57256,7 +57256,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,10 +57274,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -57288,12 +57288,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,26 +57311,26 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J15">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,10 +57348,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57098,17 +57098,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -57126,10 +57126,10 @@
         <v>81</v>
       </c>
       <c r="I10">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -57145,7 +57145,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -57163,10 +57163,10 @@
         <v>81</v>
       </c>
       <c r="I11">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J11">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -57182,7 +57182,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -57200,10 +57200,10 @@
         <v>81</v>
       </c>
       <c r="I12">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -57219,7 +57219,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,10 +57237,10 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -57256,7 +57256,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,10 +57274,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -57293,7 +57293,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -57325,12 +57325,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,26 +57348,26 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J16">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57135,17 +57135,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -57163,10 +57163,10 @@
         <v>81</v>
       </c>
       <c r="I11">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -57182,7 +57182,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -57200,10 +57200,10 @@
         <v>81</v>
       </c>
       <c r="I12">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J12">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -57219,7 +57219,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,10 +57237,10 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -57256,7 +57256,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,10 +57274,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J14">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -57293,7 +57293,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J15">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,10 +57348,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -57362,12 +57362,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57385,26 +57385,26 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J17">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -201,7 +201,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -283,7 +283,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -365,7 +365,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -17093,7 +17093,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -17170,7 +17170,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -17247,7 +17247,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -17473,7 +17473,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -17776,7 +17776,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18007,7 +18007,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -18469,7 +18469,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -19470,7 +19470,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -20672,7 +20672,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -21104,7 +21104,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -21248,7 +21248,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -21464,7 +21464,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -21680,7 +21680,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -21896,7 +21896,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -22040,7 +22040,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -22112,7 +22112,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -22256,7 +22256,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -22328,7 +22328,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -22472,7 +22472,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -22544,7 +22544,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -22899,7 +22899,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -23609,7 +23609,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -23681,7 +23681,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -23753,7 +23753,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -23897,7 +23897,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -23969,7 +23969,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -24113,7 +24113,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -24257,7 +24257,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -24329,7 +24329,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -25044,7 +25044,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -25116,7 +25116,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -25260,7 +25260,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -25327,7 +25327,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -25399,7 +25399,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -25754,7 +25754,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -26104,7 +26104,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -26248,7 +26248,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -26320,7 +26320,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -26392,7 +26392,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -26464,7 +26464,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -26680,7 +26680,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -26886,7 +26886,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -26958,7 +26958,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -27025,7 +27025,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -27097,7 +27097,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -27164,7 +27164,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -27380,7 +27380,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -27447,7 +27447,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -27519,7 +27519,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -27658,7 +27658,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -27730,7 +27730,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -28085,7 +28085,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -28157,7 +28157,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -28872,7 +28872,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -28944,7 +28944,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -29088,7 +29088,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -29160,7 +29160,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -29232,7 +29232,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -29304,7 +29304,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -29376,7 +29376,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -29448,7 +29448,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -29520,7 +29520,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -29592,7 +29592,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -29664,7 +29664,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -29736,7 +29736,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -29808,7 +29808,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
@@ -29880,7 +29880,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
@@ -29952,7 +29952,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
@@ -30168,7 +30168,7 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -30240,7 +30240,7 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
@@ -30456,7 +30456,7 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
@@ -30528,7 +30528,7 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -30600,7 +30600,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -30672,7 +30672,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -30888,7 +30888,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
@@ -30960,7 +30960,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -31032,7 +31032,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -31104,7 +31104,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -31320,7 +31320,7 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
@@ -31392,7 +31392,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -31608,7 +31608,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -31680,7 +31680,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -31824,7 +31824,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -31891,7 +31891,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -32107,7 +32107,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -32179,7 +32179,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -32323,7 +32323,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -32467,7 +32467,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -32534,7 +32534,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -32601,7 +32601,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -32673,7 +32673,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -32817,7 +32817,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -32889,7 +32889,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -32961,7 +32961,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -33033,7 +33033,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -33105,7 +33105,7 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
@@ -33172,7 +33172,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -33239,7 +33239,7 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
@@ -33311,7 +33311,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -33383,7 +33383,7 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
@@ -33599,7 +33599,7 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -33743,7 +33743,7 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -33815,7 +33815,7 @@
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
@@ -33887,7 +33887,7 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
@@ -33959,7 +33959,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -34031,7 +34031,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M454" t="inlineStr">
@@ -34247,7 +34247,7 @@
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -34391,7 +34391,7 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -34463,7 +34463,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -34535,7 +34535,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -34607,7 +34607,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -34679,7 +34679,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -34751,7 +34751,7 @@
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M462" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -34895,7 +34895,7 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M464" t="inlineStr">
@@ -34967,7 +34967,7 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
@@ -35039,7 +35039,7 @@
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -35111,7 +35111,7 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -35183,7 +35183,7 @@
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -35255,7 +35255,7 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -35399,7 +35399,7 @@
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
@@ -35471,7 +35471,7 @@
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -35543,7 +35543,7 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -35615,7 +35615,7 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -35687,7 +35687,7 @@
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -35759,7 +35759,7 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -35831,7 +35831,7 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -35903,7 +35903,7 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -36047,7 +36047,7 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
@@ -36191,7 +36191,7 @@
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M482" t="inlineStr">
@@ -36263,7 +36263,7 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
@@ -36335,7 +36335,7 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
@@ -36407,7 +36407,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
@@ -36479,7 +36479,7 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M486" t="inlineStr">
@@ -36551,7 +36551,7 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
@@ -36623,7 +36623,7 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
@@ -36695,7 +36695,7 @@
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
@@ -36767,7 +36767,7 @@
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
@@ -36839,7 +36839,7 @@
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
@@ -36911,7 +36911,7 @@
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
@@ -36983,7 +36983,7 @@
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M493" t="inlineStr">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
@@ -37127,7 +37127,7 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
@@ -37199,7 +37199,7 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M497" t="inlineStr">
@@ -37343,7 +37343,7 @@
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M498" t="inlineStr">
@@ -37415,7 +37415,7 @@
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
@@ -37487,7 +37487,7 @@
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M500" t="inlineStr">
@@ -37559,7 +37559,7 @@
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
@@ -37631,7 +37631,7 @@
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M502" t="inlineStr">
@@ -37713,7 +37713,7 @@
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
@@ -37867,7 +37867,7 @@
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M505" t="inlineStr">
@@ -37949,7 +37949,7 @@
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M506" t="inlineStr">
@@ -38031,7 +38031,7 @@
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">
@@ -38113,7 +38113,7 @@
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M508" t="inlineStr">
@@ -38195,7 +38195,7 @@
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M509" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M510" t="inlineStr">
@@ -38359,7 +38359,7 @@
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M511" t="inlineStr">
@@ -38441,7 +38441,7 @@
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M512" t="inlineStr">
@@ -38523,7 +38523,7 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
@@ -38605,7 +38605,7 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M514" t="inlineStr">
@@ -38687,7 +38687,7 @@
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M515" t="inlineStr">
@@ -38769,7 +38769,7 @@
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M516" t="inlineStr">
@@ -38816,7 +38816,7 @@
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M517" t="inlineStr">
@@ -38863,7 +38863,7 @@
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M518" t="inlineStr">
@@ -38910,7 +38910,7 @@
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M519" t="inlineStr">
@@ -38957,7 +38957,7 @@
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M520" t="inlineStr">
@@ -39004,7 +39004,7 @@
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M521" t="inlineStr">
@@ -39051,7 +39051,7 @@
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M522" t="inlineStr">
@@ -39098,7 +39098,7 @@
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M523" t="inlineStr">
@@ -39145,7 +39145,7 @@
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M524" t="inlineStr">
@@ -39192,7 +39192,7 @@
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M525" t="inlineStr">
@@ -39239,7 +39239,7 @@
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M526" t="inlineStr">
@@ -39286,7 +39286,7 @@
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M527" t="inlineStr">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M528" t="inlineStr">
@@ -39380,7 +39380,7 @@
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M529" t="inlineStr">
@@ -39427,7 +39427,7 @@
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M530" t="inlineStr">
@@ -39474,7 +39474,7 @@
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M531" t="inlineStr">
@@ -39521,7 +39521,7 @@
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M532" t="inlineStr">
@@ -39568,7 +39568,7 @@
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M533" t="inlineStr">
@@ -39615,7 +39615,7 @@
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M534" t="inlineStr">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M535" t="inlineStr">
@@ -39709,7 +39709,7 @@
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M536" t="inlineStr">
@@ -39756,7 +39756,7 @@
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M537" t="inlineStr">
@@ -39803,7 +39803,7 @@
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M538" t="inlineStr">
@@ -39850,7 +39850,7 @@
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M539" t="inlineStr">
@@ -39897,7 +39897,7 @@
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M540" t="inlineStr">
@@ -39944,7 +39944,7 @@
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M541" t="inlineStr">
@@ -39991,7 +39991,7 @@
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M542" t="inlineStr">
@@ -40038,7 +40038,7 @@
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M543" t="inlineStr">
@@ -40085,7 +40085,7 @@
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M544" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M545" t="inlineStr">
@@ -40179,7 +40179,7 @@
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M546" t="inlineStr">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M547" t="inlineStr">
@@ -40273,7 +40273,7 @@
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M548" t="inlineStr">
@@ -40320,7 +40320,7 @@
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M549" t="inlineStr">
@@ -40367,7 +40367,7 @@
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M550" t="inlineStr">
@@ -40414,7 +40414,7 @@
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M551" t="inlineStr">
@@ -40461,7 +40461,7 @@
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M552" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M553" t="inlineStr">
@@ -40555,7 +40555,7 @@
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M554" t="inlineStr">
@@ -40602,7 +40602,7 @@
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M555" t="inlineStr">
@@ -40649,7 +40649,7 @@
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M556" t="inlineStr">
@@ -40696,7 +40696,7 @@
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M557" t="inlineStr">
@@ -40743,7 +40743,7 @@
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M558" t="inlineStr">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M559" t="inlineStr">
@@ -40837,7 +40837,7 @@
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M560" t="inlineStr">
@@ -40884,7 +40884,7 @@
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M561" t="inlineStr">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M562" t="inlineStr">
@@ -40978,7 +40978,7 @@
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M563" t="inlineStr">
@@ -41025,7 +41025,7 @@
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M564" t="inlineStr">
@@ -41072,7 +41072,7 @@
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M565" t="inlineStr">
@@ -41119,7 +41119,7 @@
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M566" t="inlineStr">
@@ -41166,7 +41166,7 @@
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M567" t="inlineStr">
@@ -41213,7 +41213,7 @@
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M568" t="inlineStr">
@@ -41260,7 +41260,7 @@
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M569" t="inlineStr">
@@ -41307,7 +41307,7 @@
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M570" t="inlineStr">
@@ -41354,7 +41354,7 @@
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M571" t="inlineStr">
@@ -41401,7 +41401,7 @@
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M572" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M573" t="inlineStr">
@@ -41495,7 +41495,7 @@
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M574" t="inlineStr">
@@ -41542,7 +41542,7 @@
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M575" t="inlineStr">
@@ -41589,7 +41589,7 @@
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M576" t="inlineStr">
@@ -41636,7 +41636,7 @@
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M577" t="inlineStr">
@@ -41683,7 +41683,7 @@
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M578" t="inlineStr">
@@ -41730,7 +41730,7 @@
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M579" t="inlineStr">
@@ -41777,7 +41777,7 @@
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M580" t="inlineStr">
@@ -41824,7 +41824,7 @@
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M581" t="inlineStr">
@@ -41871,7 +41871,7 @@
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M582" t="inlineStr">
@@ -41918,7 +41918,7 @@
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M583" t="inlineStr">
@@ -41965,7 +41965,7 @@
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M584" t="inlineStr">
@@ -42012,7 +42012,7 @@
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M585" t="inlineStr">
@@ -42059,7 +42059,7 @@
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M586" t="inlineStr">
@@ -42106,7 +42106,7 @@
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M587" t="inlineStr">
@@ -42153,7 +42153,7 @@
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M588" t="inlineStr">
@@ -42200,7 +42200,7 @@
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M589" t="inlineStr">
@@ -42247,7 +42247,7 @@
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M590" t="inlineStr">
@@ -42294,7 +42294,7 @@
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M591" t="inlineStr">
@@ -42341,7 +42341,7 @@
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M592" t="inlineStr">
@@ -42388,7 +42388,7 @@
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M593" t="inlineStr">
@@ -42435,7 +42435,7 @@
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M594" t="inlineStr">
@@ -42482,7 +42482,7 @@
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M595" t="inlineStr">
@@ -42529,7 +42529,7 @@
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M596" t="inlineStr">
@@ -42576,7 +42576,7 @@
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M597" t="inlineStr">
@@ -42623,7 +42623,7 @@
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M598" t="inlineStr">
@@ -42670,7 +42670,7 @@
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M600" t="inlineStr">
@@ -42764,7 +42764,7 @@
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M601" t="inlineStr">
@@ -42811,7 +42811,7 @@
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M602" t="inlineStr">
@@ -42858,7 +42858,7 @@
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M603" t="inlineStr">
@@ -42905,7 +42905,7 @@
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M604" t="inlineStr">
@@ -42952,7 +42952,7 @@
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M605" t="inlineStr">
@@ -42999,7 +42999,7 @@
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M606" t="inlineStr">
@@ -43046,7 +43046,7 @@
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M607" t="inlineStr">
@@ -43093,7 +43093,7 @@
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M608" t="inlineStr">
@@ -43140,7 +43140,7 @@
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M609" t="inlineStr">
@@ -43187,7 +43187,7 @@
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M610" t="inlineStr">
@@ -43234,7 +43234,7 @@
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M611" t="inlineStr">
@@ -43281,7 +43281,7 @@
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M612" t="inlineStr">
@@ -43328,7 +43328,7 @@
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M613" t="inlineStr">
@@ -43375,7 +43375,7 @@
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M614" t="inlineStr">
@@ -43422,7 +43422,7 @@
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M615" t="inlineStr">
@@ -43469,7 +43469,7 @@
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M616" t="inlineStr">
@@ -43516,7 +43516,7 @@
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M617" t="inlineStr">
@@ -43563,7 +43563,7 @@
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M618" t="inlineStr">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M619" t="inlineStr">
@@ -43657,7 +43657,7 @@
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M620" t="inlineStr">
@@ -43704,7 +43704,7 @@
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M621" t="inlineStr">
@@ -43751,7 +43751,7 @@
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M622" t="inlineStr">
@@ -43798,7 +43798,7 @@
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M623" t="inlineStr">
@@ -43845,7 +43845,7 @@
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M624" t="inlineStr">
@@ -43892,7 +43892,7 @@
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M625" t="inlineStr">
@@ -43939,7 +43939,7 @@
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M626" t="inlineStr">
@@ -43986,7 +43986,7 @@
       </c>
       <c r="L627" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M627" t="inlineStr">
@@ -44033,7 +44033,7 @@
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M628" t="inlineStr">
@@ -44080,7 +44080,7 @@
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M629" t="inlineStr">
@@ -44127,7 +44127,7 @@
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M630" t="inlineStr">
@@ -44174,7 +44174,7 @@
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M631" t="inlineStr">
@@ -44221,7 +44221,7 @@
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M632" t="inlineStr">
@@ -44268,7 +44268,7 @@
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M633" t="inlineStr">
@@ -44315,7 +44315,7 @@
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M634" t="inlineStr">
@@ -44362,7 +44362,7 @@
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M635" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M636" t="inlineStr">
@@ -44456,7 +44456,7 @@
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M637" t="inlineStr">
@@ -44503,7 +44503,7 @@
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M638" t="inlineStr">
@@ -44550,7 +44550,7 @@
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M639" t="inlineStr">
@@ -44597,7 +44597,7 @@
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M640" t="inlineStr">
@@ -44644,7 +44644,7 @@
       </c>
       <c r="L641" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M641" t="inlineStr">
@@ -44691,7 +44691,7 @@
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M642" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M643" t="inlineStr">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="L644" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M644" t="inlineStr">
@@ -44832,7 +44832,7 @@
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M645" t="inlineStr">
@@ -44879,7 +44879,7 @@
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M646" t="inlineStr">
@@ -44926,7 +44926,7 @@
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M647" t="inlineStr">
@@ -44973,7 +44973,7 @@
       </c>
       <c r="L648" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M648" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M649" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -211,7 +211,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -293,7 +293,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -375,7 +375,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -17483,7 +17483,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -17786,7 +17786,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -17863,7 +17863,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -18402,7 +18402,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -18479,7 +18479,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -18556,7 +18556,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -19095,7 +19095,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -20682,7 +20682,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -21186,7 +21186,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -21258,7 +21258,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -21546,7 +21546,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -21690,7 +21690,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -21762,7 +21762,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -21906,7 +21906,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -22122,7 +22122,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -22266,7 +22266,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -22410,7 +22410,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -22693,7 +22693,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -22765,7 +22765,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -22837,7 +22837,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -23125,7 +23125,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -23197,7 +23197,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -23619,7 +23619,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -23835,7 +23835,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -24123,7 +24123,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -24195,7 +24195,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -24267,7 +24267,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
@@ -24411,7 +24411,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
@@ -24478,7 +24478,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -24622,7 +24622,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -24694,7 +24694,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
@@ -24838,7 +24838,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -24910,7 +24910,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -25054,7 +25054,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -25126,7 +25126,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
@@ -25337,7 +25337,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -25409,7 +25409,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -25553,7 +25553,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -26186,7 +26186,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -26258,7 +26258,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
@@ -26330,7 +26330,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
@@ -26402,7 +26402,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -26618,7 +26618,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -26690,7 +26690,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -26968,7 +26968,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
@@ -27035,7 +27035,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -27246,7 +27246,7 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
@@ -27318,7 +27318,7 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
@@ -27390,7 +27390,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -27457,7 +27457,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
@@ -27812,7 +27812,7 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O365" t="inlineStr">
@@ -27884,7 +27884,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
@@ -27956,7 +27956,7 @@
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -28167,7 +28167,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -28311,7 +28311,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
@@ -28450,7 +28450,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -28522,7 +28522,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
@@ -28666,7 +28666,7 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
@@ -28738,7 +28738,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -28882,7 +28882,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -28954,7 +28954,7 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
@@ -29026,7 +29026,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -29098,7 +29098,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
@@ -29170,7 +29170,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
@@ -29242,7 +29242,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
@@ -29386,7 +29386,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O388" t="inlineStr">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
@@ -29602,7 +29602,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
@@ -29674,7 +29674,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
@@ -29746,7 +29746,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
@@ -29818,7 +29818,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O394" t="inlineStr">
@@ -29962,7 +29962,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O395" t="inlineStr">
@@ -30034,7 +30034,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O396" t="inlineStr">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O398" t="inlineStr">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O399" t="inlineStr">
@@ -30322,7 +30322,7 @@
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O400" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O401" t="inlineStr">
@@ -30466,7 +30466,7 @@
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O402" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O403" t="inlineStr">
@@ -30610,7 +30610,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O404" t="inlineStr">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -30754,7 +30754,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
@@ -30826,7 +30826,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -30898,7 +30898,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
@@ -30970,7 +30970,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
@@ -31042,7 +31042,7 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O410" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O411" t="inlineStr">
@@ -31186,7 +31186,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -31258,7 +31258,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O414" t="inlineStr">
@@ -31402,7 +31402,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -31474,7 +31474,7 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O416" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
@@ -31618,7 +31618,7 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O418" t="inlineStr">
@@ -31690,7 +31690,7 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O419" t="inlineStr">
@@ -31762,7 +31762,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O420" t="inlineStr">
@@ -31834,7 +31834,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O421" t="inlineStr">
@@ -31901,7 +31901,7 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O422" t="inlineStr">
@@ -31973,7 +31973,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O423" t="inlineStr">
@@ -32045,7 +32045,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O424" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O425" t="inlineStr">
@@ -32189,7 +32189,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
@@ -32261,7 +32261,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
@@ -32333,7 +32333,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
@@ -32405,7 +32405,7 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
@@ -32477,7 +32477,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O431" t="inlineStr">
@@ -32611,7 +32611,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
@@ -32755,7 +32755,7 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O434" t="inlineStr">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O435" t="inlineStr">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O436" t="inlineStr">
@@ -32971,7 +32971,7 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
@@ -33043,7 +33043,7 @@
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O438" t="inlineStr">
@@ -33115,7 +33115,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
@@ -33182,7 +33182,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O441" t="inlineStr">
@@ -33321,7 +33321,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O442" t="inlineStr">
@@ -33393,7 +33393,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O443" t="inlineStr">
@@ -33465,7 +33465,7 @@
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O444" t="inlineStr">
@@ -33537,7 +33537,7 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
@@ -33609,7 +33609,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -33681,7 +33681,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O447" t="inlineStr">
@@ -33753,7 +33753,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
@@ -33825,7 +33825,7 @@
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O449" t="inlineStr">
@@ -33897,7 +33897,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O450" t="inlineStr">
@@ -33969,7 +33969,7 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O451" t="inlineStr">
@@ -34041,7 +34041,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O452" t="inlineStr">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
@@ -34185,7 +34185,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O454" t="inlineStr">
@@ -34257,7 +34257,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O455" t="inlineStr">
@@ -34329,7 +34329,7 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O456" t="inlineStr">
@@ -34401,7 +34401,7 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O457" t="inlineStr">
@@ -34473,7 +34473,7 @@
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O458" t="inlineStr">
@@ -34545,7 +34545,7 @@
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O459" t="inlineStr">
@@ -34617,7 +34617,7 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O460" t="inlineStr">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O461" t="inlineStr">
@@ -34761,7 +34761,7 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O462" t="inlineStr">
@@ -34833,7 +34833,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -34905,7 +34905,7 @@
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O464" t="inlineStr">
@@ -34977,7 +34977,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -35049,7 +35049,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O466" t="inlineStr">
@@ -35121,7 +35121,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O467" t="inlineStr">
@@ -35193,7 +35193,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O468" t="inlineStr">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O469" t="inlineStr">
@@ -35337,7 +35337,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
@@ -35409,7 +35409,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
@@ -35481,7 +35481,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
@@ -35553,7 +35553,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
@@ -35625,7 +35625,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
@@ -35697,7 +35697,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
@@ -35769,7 +35769,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
@@ -35841,7 +35841,7 @@
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O477" t="inlineStr">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
@@ -35985,7 +35985,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
@@ -36057,7 +36057,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O481" t="inlineStr">
@@ -36201,7 +36201,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O482" t="inlineStr">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -36345,7 +36345,7 @@
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O484" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O485" t="inlineStr">
@@ -36489,7 +36489,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
@@ -36561,7 +36561,7 @@
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O487" t="inlineStr">
@@ -36633,7 +36633,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
@@ -36705,7 +36705,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
@@ -36777,7 +36777,7 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O490" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O491" t="inlineStr">
@@ -36921,7 +36921,7 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
@@ -36993,7 +36993,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O493" t="inlineStr">
@@ -37065,7 +37065,7 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O494" t="inlineStr">
@@ -37137,7 +37137,7 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O495" t="inlineStr">
@@ -37209,7 +37209,7 @@
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O496" t="inlineStr">
@@ -37281,7 +37281,7 @@
       </c>
       <c r="N497" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O497" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O498" t="inlineStr">
@@ -37425,7 +37425,7 @@
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O499" t="inlineStr">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O500" t="inlineStr">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O501" t="inlineStr">
@@ -37641,7 +37641,7 @@
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O502" t="inlineStr">
@@ -37723,7 +37723,7 @@
       </c>
       <c r="N503" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O503" t="inlineStr">
@@ -37800,7 +37800,7 @@
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O504" t="inlineStr">
@@ -37877,7 +37877,7 @@
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O505" t="inlineStr">
@@ -37959,7 +37959,7 @@
       </c>
       <c r="N506" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O506" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O507" t="inlineStr">
@@ -38123,7 +38123,7 @@
       </c>
       <c r="N508" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O508" t="inlineStr">
@@ -38205,7 +38205,7 @@
       </c>
       <c r="N509" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O509" t="inlineStr">
@@ -38287,7 +38287,7 @@
       </c>
       <c r="N510" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O510" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="N511" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O511" t="inlineStr">
@@ -38451,7 +38451,7 @@
       </c>
       <c r="N512" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O512" t="inlineStr">
@@ -38533,7 +38533,7 @@
       </c>
       <c r="N513" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O513" t="inlineStr">
@@ -38615,7 +38615,7 @@
       </c>
       <c r="N514" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O514" t="inlineStr">
@@ -38697,7 +38697,7 @@
       </c>
       <c r="N515" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O515" t="inlineStr">
@@ -38779,7 +38779,7 @@
       </c>
       <c r="N516" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O516" t="inlineStr">
@@ -38826,7 +38826,7 @@
       </c>
       <c r="N517" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O517" t="inlineStr">
@@ -38873,7 +38873,7 @@
       </c>
       <c r="N518" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O518" t="inlineStr">
@@ -38920,7 +38920,7 @@
       </c>
       <c r="N519" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O519" t="inlineStr">
@@ -38967,7 +38967,7 @@
       </c>
       <c r="N520" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O520" t="inlineStr">
@@ -39014,7 +39014,7 @@
       </c>
       <c r="N521" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O521" t="inlineStr">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="N522" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O522" t="inlineStr">
@@ -39108,7 +39108,7 @@
       </c>
       <c r="N523" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O523" t="inlineStr">
@@ -39155,7 +39155,7 @@
       </c>
       <c r="N524" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O524" t="inlineStr">
@@ -39202,7 +39202,7 @@
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O525" t="inlineStr">
@@ -39249,7 +39249,7 @@
       </c>
       <c r="N526" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O526" t="inlineStr">
@@ -39296,7 +39296,7 @@
       </c>
       <c r="N527" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O527" t="inlineStr">
@@ -39343,7 +39343,7 @@
       </c>
       <c r="N528" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O528" t="inlineStr">
@@ -39390,7 +39390,7 @@
       </c>
       <c r="N529" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O529" t="inlineStr">
@@ -39437,7 +39437,7 @@
       </c>
       <c r="N530" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O530" t="inlineStr">
@@ -39484,7 +39484,7 @@
       </c>
       <c r="N531" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O531" t="inlineStr">
@@ -39531,7 +39531,7 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O532" t="inlineStr">
@@ -39578,7 +39578,7 @@
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O533" t="inlineStr">
@@ -39625,7 +39625,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O534" t="inlineStr">
@@ -39672,7 +39672,7 @@
       </c>
       <c r="N535" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O535" t="inlineStr">
@@ -39719,7 +39719,7 @@
       </c>
       <c r="N536" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O536" t="inlineStr">
@@ -39766,7 +39766,7 @@
       </c>
       <c r="N537" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O537" t="inlineStr">
@@ -39813,7 +39813,7 @@
       </c>
       <c r="N538" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O538" t="inlineStr">
@@ -39860,7 +39860,7 @@
       </c>
       <c r="N539" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O539" t="inlineStr">
@@ -39907,7 +39907,7 @@
       </c>
       <c r="N540" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O540" t="inlineStr">
@@ -39954,7 +39954,7 @@
       </c>
       <c r="N541" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O541" t="inlineStr">
@@ -40001,7 +40001,7 @@
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O542" t="inlineStr">
@@ -40048,7 +40048,7 @@
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O543" t="inlineStr">
@@ -40095,7 +40095,7 @@
       </c>
       <c r="N544" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O544" t="inlineStr">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="N545" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O545" t="inlineStr">
@@ -40189,7 +40189,7 @@
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O546" t="inlineStr">
@@ -40236,7 +40236,7 @@
       </c>
       <c r="N547" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O547" t="inlineStr">
@@ -40283,7 +40283,7 @@
       </c>
       <c r="N548" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O548" t="inlineStr">
@@ -40330,7 +40330,7 @@
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O549" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O550" t="inlineStr">
@@ -40424,7 +40424,7 @@
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O551" t="inlineStr">
@@ -40471,7 +40471,7 @@
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O552" t="inlineStr">
@@ -40518,7 +40518,7 @@
       </c>
       <c r="N553" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O553" t="inlineStr">
@@ -40565,7 +40565,7 @@
       </c>
       <c r="N554" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O554" t="inlineStr">
@@ -40612,7 +40612,7 @@
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O555" t="inlineStr">
@@ -40659,7 +40659,7 @@
       </c>
       <c r="N556" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O556" t="inlineStr">
@@ -40706,7 +40706,7 @@
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O557" t="inlineStr">
@@ -40753,7 +40753,7 @@
       </c>
       <c r="N558" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O558" t="inlineStr">
@@ -40800,7 +40800,7 @@
       </c>
       <c r="N559" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O559" t="inlineStr">
@@ -40847,7 +40847,7 @@
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O560" t="inlineStr">
@@ -40894,7 +40894,7 @@
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O561" t="inlineStr">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="N562" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O562" t="inlineStr">
@@ -40988,7 +40988,7 @@
       </c>
       <c r="N563" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O563" t="inlineStr">
@@ -41035,7 +41035,7 @@
       </c>
       <c r="N564" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O564" t="inlineStr">
@@ -41082,7 +41082,7 @@
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O565" t="inlineStr">
@@ -41129,7 +41129,7 @@
       </c>
       <c r="N566" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O566" t="inlineStr">
@@ -41176,7 +41176,7 @@
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O567" t="inlineStr">
@@ -41223,7 +41223,7 @@
       </c>
       <c r="N568" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O568" t="inlineStr">
@@ -41270,7 +41270,7 @@
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O569" t="inlineStr">
@@ -41317,7 +41317,7 @@
       </c>
       <c r="N570" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O570" t="inlineStr">
@@ -41364,7 +41364,7 @@
       </c>
       <c r="N571" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O571" t="inlineStr">
@@ -41411,7 +41411,7 @@
       </c>
       <c r="N572" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O572" t="inlineStr">
@@ -41458,7 +41458,7 @@
       </c>
       <c r="N573" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O573" t="inlineStr">
@@ -41505,7 +41505,7 @@
       </c>
       <c r="N574" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O574" t="inlineStr">
@@ -41552,7 +41552,7 @@
       </c>
       <c r="N575" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O575" t="inlineStr">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="N576" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O576" t="inlineStr">
@@ -41646,7 +41646,7 @@
       </c>
       <c r="N577" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O577" t="inlineStr">
@@ -41693,7 +41693,7 @@
       </c>
       <c r="N578" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O578" t="inlineStr">
@@ -41740,7 +41740,7 @@
       </c>
       <c r="N579" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O579" t="inlineStr">
@@ -41787,7 +41787,7 @@
       </c>
       <c r="N580" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O580" t="inlineStr">
@@ -41834,7 +41834,7 @@
       </c>
       <c r="N581" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O581" t="inlineStr">
@@ -41881,7 +41881,7 @@
       </c>
       <c r="N582" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O582" t="inlineStr">
@@ -41928,7 +41928,7 @@
       </c>
       <c r="N583" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O583" t="inlineStr">
@@ -41975,7 +41975,7 @@
       </c>
       <c r="N584" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O584" t="inlineStr">
@@ -42022,7 +42022,7 @@
       </c>
       <c r="N585" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O585" t="inlineStr">
@@ -42069,7 +42069,7 @@
       </c>
       <c r="N586" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O586" t="inlineStr">
@@ -42116,7 +42116,7 @@
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O587" t="inlineStr">
@@ -42163,7 +42163,7 @@
       </c>
       <c r="N588" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O588" t="inlineStr">
@@ -42210,7 +42210,7 @@
       </c>
       <c r="N589" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O589" t="inlineStr">
@@ -42257,7 +42257,7 @@
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O590" t="inlineStr">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O591" t="inlineStr">
@@ -42351,7 +42351,7 @@
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O592" t="inlineStr">
@@ -42398,7 +42398,7 @@
       </c>
       <c r="N593" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O593" t="inlineStr">
@@ -42445,7 +42445,7 @@
       </c>
       <c r="N594" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O594" t="inlineStr">
@@ -42492,7 +42492,7 @@
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O595" t="inlineStr">
@@ -42539,7 +42539,7 @@
       </c>
       <c r="N596" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O596" t="inlineStr">
@@ -42586,7 +42586,7 @@
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O597" t="inlineStr">
@@ -42633,7 +42633,7 @@
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
@@ -42680,7 +42680,7 @@
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
@@ -42727,7 +42727,7 @@
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
@@ -42774,7 +42774,7 @@
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
@@ -42821,7 +42821,7 @@
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
@@ -42868,7 +42868,7 @@
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
@@ -42915,7 +42915,7 @@
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O604" t="inlineStr">
@@ -42962,7 +42962,7 @@
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
@@ -43009,7 +43009,7 @@
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
@@ -43056,7 +43056,7 @@
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O607" t="inlineStr">
@@ -43103,7 +43103,7 @@
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
@@ -43150,7 +43150,7 @@
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O609" t="inlineStr">
@@ -43197,7 +43197,7 @@
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O610" t="inlineStr">
@@ -43244,7 +43244,7 @@
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O611" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O612" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O613" t="inlineStr">
@@ -43385,7 +43385,7 @@
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O614" t="inlineStr">
@@ -43432,7 +43432,7 @@
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O615" t="inlineStr">
@@ -43479,7 +43479,7 @@
       </c>
       <c r="N616" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O616" t="inlineStr">
@@ -43526,7 +43526,7 @@
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O617" t="inlineStr">
@@ -43573,7 +43573,7 @@
       </c>
       <c r="N618" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O618" t="inlineStr">
@@ -43620,7 +43620,7 @@
       </c>
       <c r="N619" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O619" t="inlineStr">
@@ -43667,7 +43667,7 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O620" t="inlineStr">
@@ -43714,7 +43714,7 @@
       </c>
       <c r="N621" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O621" t="inlineStr">
@@ -43761,7 +43761,7 @@
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O622" t="inlineStr">
@@ -43808,7 +43808,7 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O623" t="inlineStr">
@@ -43855,7 +43855,7 @@
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O624" t="inlineStr">
@@ -43902,7 +43902,7 @@
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O625" t="inlineStr">
@@ -43949,7 +43949,7 @@
       </c>
       <c r="N626" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O626" t="inlineStr">
@@ -43996,7 +43996,7 @@
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O627" t="inlineStr">
@@ -44043,7 +44043,7 @@
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O628" t="inlineStr">
@@ -44090,7 +44090,7 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O629" t="inlineStr">
@@ -44137,7 +44137,7 @@
       </c>
       <c r="N630" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O630" t="inlineStr">
@@ -44184,7 +44184,7 @@
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O631" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="N632" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O632" t="inlineStr">
@@ -44278,7 +44278,7 @@
       </c>
       <c r="N633" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O633" t="inlineStr">
@@ -44325,7 +44325,7 @@
       </c>
       <c r="N634" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O634" t="inlineStr">
@@ -44372,7 +44372,7 @@
       </c>
       <c r="N635" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O635" t="inlineStr">
@@ -44419,7 +44419,7 @@
       </c>
       <c r="N636" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O636" t="inlineStr">
@@ -44466,7 +44466,7 @@
       </c>
       <c r="N637" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O637" t="inlineStr">
@@ -44513,7 +44513,7 @@
       </c>
       <c r="N638" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O638" t="inlineStr">
@@ -44560,7 +44560,7 @@
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O639" t="inlineStr">
@@ -44607,7 +44607,7 @@
       </c>
       <c r="N640" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
@@ -44654,7 +44654,7 @@
       </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
@@ -44701,7 +44701,7 @@
       </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
@@ -44748,7 +44748,7 @@
       </c>
       <c r="N643" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O643" t="inlineStr">
@@ -44795,7 +44795,7 @@
       </c>
       <c r="N644" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O644" t="inlineStr">
@@ -44842,7 +44842,7 @@
       </c>
       <c r="N645" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
@@ -44889,7 +44889,7 @@
       </c>
       <c r="N646" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
@@ -44936,7 +44936,7 @@
       </c>
       <c r="N647" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
@@ -44983,7 +44983,7 @@
       </c>
       <c r="N648" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O648" t="inlineStr">
@@ -45030,7 +45030,7 @@
       </c>
       <c r="N649" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -216,7 +216,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -298,7 +298,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -380,7 +380,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -15896,7 +15896,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -17642,7 +17642,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
@@ -18022,7 +18022,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
@@ -18407,7 +18407,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -19485,7 +19485,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -20831,7 +20831,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -20903,7 +20903,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -21119,7 +21119,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -21335,7 +21335,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -21623,7 +21623,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -21839,7 +21839,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -22271,7 +22271,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -22698,7 +22698,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -22986,7 +22986,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -23552,7 +23552,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -23624,7 +23624,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -23696,7 +23696,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -23768,7 +23768,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -24056,7 +24056,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -24200,7 +24200,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -24272,7 +24272,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -24416,7 +24416,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -24483,7 +24483,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -24555,7 +24555,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -24843,7 +24843,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -24915,7 +24915,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -25059,7 +25059,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -25275,7 +25275,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -25625,7 +25625,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -25769,7 +25769,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -26191,7 +26191,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -26263,7 +26263,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -26407,7 +26407,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -26551,7 +26551,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -26762,7 +26762,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -26829,7 +26829,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -26973,7 +26973,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -27040,7 +27040,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -27112,7 +27112,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -27179,7 +27179,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -27534,7 +27534,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -27606,7 +27606,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -27673,7 +27673,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -27745,7 +27745,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -27817,7 +27817,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
@@ -27889,7 +27889,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -27961,7 +27961,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -28100,7 +28100,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
@@ -28172,7 +28172,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
@@ -28383,7 +28383,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
@@ -28527,7 +28527,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R375" t="inlineStr">
@@ -28815,7 +28815,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R379" t="inlineStr">
@@ -28887,7 +28887,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R380" t="inlineStr">
@@ -28959,7 +28959,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R381" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R382" t="inlineStr">
@@ -29103,7 +29103,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R383" t="inlineStr">
@@ -29175,7 +29175,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R384" t="inlineStr">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R385" t="inlineStr">
@@ -29319,7 +29319,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R386" t="inlineStr">
@@ -29391,7 +29391,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R387" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R388" t="inlineStr">
@@ -29535,7 +29535,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R389" t="inlineStr">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R390" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R391" t="inlineStr">
@@ -29751,7 +29751,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R392" t="inlineStr">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R393" t="inlineStr">
@@ -29895,7 +29895,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R394" t="inlineStr">
@@ -29967,7 +29967,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R395" t="inlineStr">
@@ -30039,7 +30039,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R396" t="inlineStr">
@@ -30111,7 +30111,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R397" t="inlineStr">
@@ -30183,7 +30183,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R398" t="inlineStr">
@@ -30255,7 +30255,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R399" t="inlineStr">
@@ -30327,7 +30327,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R400" t="inlineStr">
@@ -30399,7 +30399,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R401" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R402" t="inlineStr">
@@ -30543,7 +30543,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R403" t="inlineStr">
@@ -30615,7 +30615,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R404" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R405" t="inlineStr">
@@ -30759,7 +30759,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R406" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R407" t="inlineStr">
@@ -30903,7 +30903,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R408" t="inlineStr">
@@ -30975,7 +30975,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R409" t="inlineStr">
@@ -31047,7 +31047,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R410" t="inlineStr">
@@ -31119,7 +31119,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R411" t="inlineStr">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R412" t="inlineStr">
@@ -31263,7 +31263,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R413" t="inlineStr">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R414" t="inlineStr">
@@ -31407,7 +31407,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R415" t="inlineStr">
@@ -31479,7 +31479,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R416" t="inlineStr">
@@ -31551,7 +31551,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R417" t="inlineStr">
@@ -31623,7 +31623,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R418" t="inlineStr">
@@ -31695,7 +31695,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R419" t="inlineStr">
@@ -31767,7 +31767,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R420" t="inlineStr">
@@ -31839,7 +31839,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R421" t="inlineStr">
@@ -31906,7 +31906,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R422" t="inlineStr">
@@ -31978,7 +31978,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R423" t="inlineStr">
@@ -32050,7 +32050,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R424" t="inlineStr">
@@ -32122,7 +32122,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R425" t="inlineStr">
@@ -32194,7 +32194,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R426" t="inlineStr">
@@ -32266,7 +32266,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R427" t="inlineStr">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R428" t="inlineStr">
@@ -32410,7 +32410,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R429" t="inlineStr">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R430" t="inlineStr">
@@ -32549,7 +32549,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R431" t="inlineStr">
@@ -32616,7 +32616,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R432" t="inlineStr">
@@ -32688,7 +32688,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R433" t="inlineStr">
@@ -32760,7 +32760,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -32832,7 +32832,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R435" t="inlineStr">
@@ -32904,7 +32904,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R436" t="inlineStr">
@@ -32976,7 +32976,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R437" t="inlineStr">
@@ -33048,7 +33048,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R438" t="inlineStr">
@@ -33120,7 +33120,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R439" t="inlineStr">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R440" t="inlineStr">
@@ -33254,7 +33254,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R441" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R442" t="inlineStr">
@@ -33398,7 +33398,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R443" t="inlineStr">
@@ -33470,7 +33470,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R444" t="inlineStr">
@@ -33542,7 +33542,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R445" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R446" t="inlineStr">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R447" t="inlineStr">
@@ -33758,7 +33758,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R448" t="inlineStr">
@@ -33830,7 +33830,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R449" t="inlineStr">
@@ -33902,7 +33902,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R450" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R451" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R452" t="inlineStr">
@@ -34118,7 +34118,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R453" t="inlineStr">
@@ -34190,7 +34190,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R454" t="inlineStr">
@@ -34262,7 +34262,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R455" t="inlineStr">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R456" t="inlineStr">
@@ -34406,7 +34406,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R457" t="inlineStr">
@@ -34478,7 +34478,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R458" t="inlineStr">
@@ -34550,7 +34550,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R459" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R460" t="inlineStr">
@@ -34694,7 +34694,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R461" t="inlineStr">
@@ -34766,7 +34766,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R462" t="inlineStr">
@@ -34838,7 +34838,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R463" t="inlineStr">
@@ -34910,7 +34910,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R464" t="inlineStr">
@@ -34982,7 +34982,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R465" t="inlineStr">
@@ -35054,7 +35054,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R466" t="inlineStr">
@@ -35126,7 +35126,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R467" t="inlineStr">
@@ -35198,7 +35198,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R468" t="inlineStr">
@@ -35270,7 +35270,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R469" t="inlineStr">
@@ -35342,7 +35342,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R470" t="inlineStr">
@@ -35414,7 +35414,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R471" t="inlineStr">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R472" t="inlineStr">
@@ -35558,7 +35558,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R473" t="inlineStr">
@@ -35630,7 +35630,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R474" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R475" t="inlineStr">
@@ -35774,7 +35774,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R476" t="inlineStr">
@@ -35846,7 +35846,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R477" t="inlineStr">
@@ -35918,7 +35918,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R478" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R479" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R480" t="inlineStr">
@@ -36134,7 +36134,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R481" t="inlineStr">
@@ -36206,7 +36206,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R482" t="inlineStr">
@@ -36278,7 +36278,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R483" t="inlineStr">
@@ -36350,7 +36350,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R484" t="inlineStr">
@@ -36422,7 +36422,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R485" t="inlineStr">
@@ -36494,7 +36494,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R486" t="inlineStr">
@@ -36566,7 +36566,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R487" t="inlineStr">
@@ -36638,7 +36638,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R488" t="inlineStr">
@@ -36710,7 +36710,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R489" t="inlineStr">
@@ -36782,7 +36782,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R490" t="inlineStr">
@@ -36854,7 +36854,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R491" t="inlineStr">
@@ -36926,7 +36926,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R492" t="inlineStr">
@@ -36998,7 +36998,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R493" t="inlineStr">
@@ -37070,7 +37070,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R494" t="inlineStr">
@@ -37142,7 +37142,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R495" t="inlineStr">
@@ -37214,7 +37214,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R496" t="inlineStr">
@@ -37286,7 +37286,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R497" t="inlineStr">
@@ -37358,7 +37358,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R498" t="inlineStr">
@@ -37430,7 +37430,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R499" t="inlineStr">
@@ -37502,7 +37502,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R500" t="inlineStr">
@@ -37574,7 +37574,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R501" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R502" t="inlineStr">
@@ -37805,7 +37805,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R504" t="inlineStr">
@@ -37882,7 +37882,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R505" t="inlineStr">
@@ -37964,7 +37964,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R506" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R507" t="inlineStr">
@@ -38292,7 +38292,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R510" t="inlineStr">
@@ -38374,7 +38374,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R511" t="inlineStr">
@@ -38456,7 +38456,7 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R512" t="inlineStr">
@@ -38538,7 +38538,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R513" t="inlineStr">
@@ -38620,7 +38620,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R514" t="inlineStr">
@@ -38702,7 +38702,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R515" t="inlineStr">
@@ -38784,7 +38784,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R516" t="inlineStr">
@@ -38831,7 +38831,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R517" t="inlineStr">
@@ -38878,7 +38878,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R518" t="inlineStr">
@@ -38925,7 +38925,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R519" t="inlineStr">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R520" t="inlineStr">
@@ -39019,7 +39019,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R521" t="inlineStr">
@@ -39066,7 +39066,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R522" t="inlineStr">
@@ -39113,7 +39113,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R523" t="inlineStr">
@@ -39160,7 +39160,7 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R524" t="inlineStr">
@@ -39207,7 +39207,7 @@
       </c>
       <c r="O525" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R525" t="inlineStr">
@@ -39254,7 +39254,7 @@
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R526" t="inlineStr">
@@ -39301,7 +39301,7 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R527" t="inlineStr">
@@ -39348,7 +39348,7 @@
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R528" t="inlineStr">
@@ -39395,7 +39395,7 @@
       </c>
       <c r="O529" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R529" t="inlineStr">
@@ -39442,7 +39442,7 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R530" t="inlineStr">
@@ -39489,7 +39489,7 @@
       </c>
       <c r="O531" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R531" t="inlineStr">
@@ -39536,7 +39536,7 @@
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R532" t="inlineStr">
@@ -39583,7 +39583,7 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R533" t="inlineStr">
@@ -39630,7 +39630,7 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R534" t="inlineStr">
@@ -39677,7 +39677,7 @@
       </c>
       <c r="O535" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R535" t="inlineStr">
@@ -39724,7 +39724,7 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R536" t="inlineStr">
@@ -39771,7 +39771,7 @@
       </c>
       <c r="O537" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R537" t="inlineStr">
@@ -39818,7 +39818,7 @@
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R538" t="inlineStr">
@@ -39865,7 +39865,7 @@
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R539" t="inlineStr">
@@ -39912,7 +39912,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R540" t="inlineStr">
@@ -39959,7 +39959,7 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R541" t="inlineStr">
@@ -40006,7 +40006,7 @@
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R542" t="inlineStr">
@@ -40053,7 +40053,7 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R543" t="inlineStr">
@@ -40100,7 +40100,7 @@
       </c>
       <c r="O544" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R544" t="inlineStr">
@@ -40147,7 +40147,7 @@
       </c>
       <c r="O545" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R545" t="inlineStr">
@@ -40194,7 +40194,7 @@
       </c>
       <c r="O546" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R546" t="inlineStr">
@@ -40241,7 +40241,7 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R547" t="inlineStr">
@@ -40288,7 +40288,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R548" t="inlineStr">
@@ -40335,7 +40335,7 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R549" t="inlineStr">
@@ -40382,7 +40382,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R550" t="inlineStr">
@@ -40429,7 +40429,7 @@
       </c>
       <c r="O551" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R551" t="inlineStr">
@@ -40476,7 +40476,7 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R552" t="inlineStr">
@@ -40523,7 +40523,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R553" t="inlineStr">
@@ -40570,7 +40570,7 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R554" t="inlineStr">
@@ -40617,7 +40617,7 @@
       </c>
       <c r="O555" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R555" t="inlineStr">
@@ -40664,7 +40664,7 @@
       </c>
       <c r="O556" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R556" t="inlineStr">
@@ -40711,7 +40711,7 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R557" t="inlineStr">
@@ -40758,7 +40758,7 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R558" t="inlineStr">
@@ -40805,7 +40805,7 @@
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R559" t="inlineStr">
@@ -40852,7 +40852,7 @@
       </c>
       <c r="O560" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R560" t="inlineStr">
@@ -40899,7 +40899,7 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R561" t="inlineStr">
@@ -40946,7 +40946,7 @@
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R562" t="inlineStr">
@@ -40993,7 +40993,7 @@
       </c>
       <c r="O563" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R563" t="inlineStr">
@@ -41040,7 +41040,7 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R564" t="inlineStr">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R565" t="inlineStr">
@@ -41134,7 +41134,7 @@
       </c>
       <c r="O566" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R566" t="inlineStr">
@@ -41181,7 +41181,7 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R567" t="inlineStr">
@@ -41228,7 +41228,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R568" t="inlineStr">
@@ -41275,7 +41275,7 @@
       </c>
       <c r="O569" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R569" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R570" t="inlineStr">
@@ -41369,7 +41369,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R571" t="inlineStr">
@@ -41416,7 +41416,7 @@
       </c>
       <c r="O572" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R572" t="inlineStr">
@@ -41463,7 +41463,7 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R573" t="inlineStr">
@@ -41510,7 +41510,7 @@
       </c>
       <c r="O574" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R574" t="inlineStr">
@@ -41557,7 +41557,7 @@
       </c>
       <c r="O575" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R575" t="inlineStr">
@@ -41604,7 +41604,7 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R576" t="inlineStr">
@@ -41651,7 +41651,7 @@
       </c>
       <c r="O577" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R577" t="inlineStr">
@@ -41698,7 +41698,7 @@
       </c>
       <c r="O578" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R578" t="inlineStr">
@@ -41745,7 +41745,7 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R579" t="inlineStr">
@@ -41792,7 +41792,7 @@
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R580" t="inlineStr">
@@ -41839,7 +41839,7 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R581" t="inlineStr">
@@ -41886,7 +41886,7 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R582" t="inlineStr">
@@ -41933,7 +41933,7 @@
       </c>
       <c r="O583" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R583" t="inlineStr">
@@ -41980,7 +41980,7 @@
       </c>
       <c r="O584" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R584" t="inlineStr">
@@ -42027,7 +42027,7 @@
       </c>
       <c r="O585" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R585" t="inlineStr">
@@ -42074,7 +42074,7 @@
       </c>
       <c r="O586" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R586" t="inlineStr">
@@ -42121,7 +42121,7 @@
       </c>
       <c r="O587" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R587" t="inlineStr">
@@ -42168,7 +42168,7 @@
       </c>
       <c r="O588" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R588" t="inlineStr">
@@ -42215,7 +42215,7 @@
       </c>
       <c r="O589" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R589" t="inlineStr">
@@ -42262,7 +42262,7 @@
       </c>
       <c r="O590" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R590" t="inlineStr">
@@ -42309,7 +42309,7 @@
       </c>
       <c r="O591" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R591" t="inlineStr">
@@ -42356,7 +42356,7 @@
       </c>
       <c r="O592" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R592" t="inlineStr">
@@ -42403,7 +42403,7 @@
       </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R593" t="inlineStr">
@@ -42450,7 +42450,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R594" t="inlineStr">
@@ -42497,7 +42497,7 @@
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R595" t="inlineStr">
@@ -42544,7 +42544,7 @@
       </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R596" t="inlineStr">
@@ -42591,7 +42591,7 @@
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R597" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R598" t="inlineStr">
@@ -42685,7 +42685,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R599" t="inlineStr">
@@ -42732,7 +42732,7 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R600" t="inlineStr">
@@ -42779,7 +42779,7 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R601" t="inlineStr">
@@ -42826,7 +42826,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R602" t="inlineStr">
@@ -42873,7 +42873,7 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R603" t="inlineStr">
@@ -42920,7 +42920,7 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R604" t="inlineStr">
@@ -42967,7 +42967,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R605" t="inlineStr">
@@ -43014,7 +43014,7 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R606" t="inlineStr">
@@ -43061,7 +43061,7 @@
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R607" t="inlineStr">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R608" t="inlineStr">
@@ -43155,7 +43155,7 @@
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R609" t="inlineStr">
@@ -43202,7 +43202,7 @@
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R610" t="inlineStr">
@@ -43249,7 +43249,7 @@
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R611" t="inlineStr">
@@ -43296,7 +43296,7 @@
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R612" t="inlineStr">
@@ -43343,7 +43343,7 @@
       </c>
       <c r="O613" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R613" t="inlineStr">
@@ -43390,7 +43390,7 @@
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R614" t="inlineStr">
@@ -43437,7 +43437,7 @@
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R615" t="inlineStr">
@@ -43484,7 +43484,7 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R616" t="inlineStr">
@@ -43531,7 +43531,7 @@
       </c>
       <c r="O617" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R617" t="inlineStr">
@@ -43578,7 +43578,7 @@
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R618" t="inlineStr">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="O619" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R619" t="inlineStr">
@@ -43672,7 +43672,7 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R620" t="inlineStr">
@@ -43719,7 +43719,7 @@
       </c>
       <c r="O621" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R621" t="inlineStr">
@@ -43766,7 +43766,7 @@
       </c>
       <c r="O622" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R622" t="inlineStr">
@@ -43813,7 +43813,7 @@
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R623" t="inlineStr">
@@ -43860,7 +43860,7 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R624" t="inlineStr">
@@ -43907,7 +43907,7 @@
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R625" t="inlineStr">
@@ -43954,7 +43954,7 @@
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R626" t="inlineStr">
@@ -44001,7 +44001,7 @@
       </c>
       <c r="O627" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R627" t="inlineStr">
@@ -44048,7 +44048,7 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R628" t="inlineStr">
@@ -44095,7 +44095,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R629" t="inlineStr">
@@ -44142,7 +44142,7 @@
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R630" t="inlineStr">
@@ -44189,7 +44189,7 @@
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R631" t="inlineStr">
@@ -44236,7 +44236,7 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R632" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="O633" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R633" t="inlineStr">
@@ -44330,7 +44330,7 @@
       </c>
       <c r="O634" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R634" t="inlineStr">
@@ -44377,7 +44377,7 @@
       </c>
       <c r="O635" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R635" t="inlineStr">
@@ -44424,7 +44424,7 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R636" t="inlineStr">
@@ -44471,7 +44471,7 @@
       </c>
       <c r="O637" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R637" t="inlineStr">
@@ -44518,7 +44518,7 @@
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R638" t="inlineStr">
@@ -44565,7 +44565,7 @@
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R639" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R640" t="inlineStr">
@@ -44659,7 +44659,7 @@
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R641" t="inlineStr">
@@ -44706,7 +44706,7 @@
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R642" t="inlineStr">
@@ -44753,7 +44753,7 @@
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R643" t="inlineStr">
@@ -44800,7 +44800,7 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R644" t="inlineStr">
@@ -44847,7 +44847,7 @@
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R645" t="inlineStr">
@@ -44894,7 +44894,7 @@
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R646" t="inlineStr">
@@ -44941,7 +44941,7 @@
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R647" t="inlineStr">
@@ -44988,7 +44988,7 @@
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R648" t="inlineStr">
@@ -45035,7 +45035,7 @@
       </c>
       <c r="O649" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R649" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57428,6 +57428,228 @@
         <v>81</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChIP Box</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>9</v>
+      </c>
+      <c r="G19">
+        <v>9</v>
+      </c>
+      <c r="H19">
+        <v>81</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChIP Box -2-</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>9</v>
+      </c>
+      <c r="H20">
+        <v>81</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut -20 -2-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>9</v>
+      </c>
+      <c r="G21">
+        <v>9</v>
+      </c>
+      <c r="H21">
+        <v>81</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <v>9</v>
+      </c>
+      <c r="H22">
+        <v>81</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unkown FOR NOW</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>9</v>
+      </c>
+      <c r="G23">
+        <v>9</v>
+      </c>
+      <c r="H23">
+        <v>81</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No use</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>9</v>
+      </c>
+      <c r="H24">
+        <v>81</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57172,17 +57172,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -57200,10 +57200,10 @@
         <v>81</v>
       </c>
       <c r="I12">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -57219,7 +57219,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,10 +57237,10 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J13">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -57256,7 +57256,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,10 +57274,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -57293,7 +57293,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,10 +57348,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J16">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -57367,7 +57367,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57385,10 +57385,10 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -57399,12 +57399,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57422,26 +57422,26 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J18">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57209,17 +57209,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,10 +57237,10 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
@@ -57256,7 +57256,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,10 +57274,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J14">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -57293,7 +57293,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,10 +57348,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -57367,7 +57367,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57385,10 +57385,10 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J17">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -57404,7 +57404,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57422,10 +57422,10 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -57436,12 +57436,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -57459,26 +57459,26 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J19">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57246,17 +57246,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,10 +57274,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -57293,7 +57293,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J15">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,10 +57348,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -57367,7 +57367,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57385,10 +57385,10 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J17">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -57404,7 +57404,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57422,10 +57422,10 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J18">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -57441,7 +57441,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -57459,10 +57459,10 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -57473,12 +57473,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -57496,26 +57496,26 @@
         <v>81</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J20">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57283,17 +57283,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,10 +57348,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J16">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
@@ -57367,7 +57367,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57385,10 +57385,10 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -57404,7 +57404,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57422,10 +57422,10 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J18">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -57441,7 +57441,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -57459,10 +57459,10 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J19">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -57478,7 +57478,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -57496,10 +57496,10 @@
         <v>81</v>
       </c>
       <c r="I20">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -57510,12 +57510,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -57533,26 +57533,26 @@
         <v>81</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J21">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57209,17 +57209,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,26 +57237,26 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J13">
-        <v>81</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,26 +57274,26 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J14">
-        <v>81</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J15">
-        <v>81</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,10 +57348,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="J16">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -57367,7 +57367,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57385,10 +57385,10 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="J17">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -57404,7 +57404,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57422,10 +57422,10 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -57436,12 +57436,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -57459,26 +57459,26 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -57496,26 +57496,26 @@
         <v>81</v>
       </c>
       <c r="I20">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -57533,26 +57533,26 @@
         <v>81</v>
       </c>
       <c r="I21">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57182,7 +57182,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -57478,7 +57478,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57182,7 +57182,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -57209,17 +57209,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,10 +57237,10 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
@@ -57256,7 +57256,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,10 +57274,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J14">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -57293,7 +57293,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,10 +57348,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -57367,7 +57367,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57385,10 +57385,10 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J17">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -57404,7 +57404,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57422,10 +57422,10 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -57436,12 +57436,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -57459,26 +57459,26 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J19">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -56802,7 +56802,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -56812,7 +56812,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CAA CELLS</t>
+          <t xml:space="preserve">LiqNitro 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -56830,16 +56830,16 @@
         <v>81</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>81</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -56849,7 +56849,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">LiqNitro 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -56867,26 +56867,26 @@
         <v>81</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J3">
-        <v>81</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -56913,17 +56913,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONGOING</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -56950,7 +56950,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -56960,7 +56960,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -56987,17 +56987,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -57024,7 +57024,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquid Nitrogen</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -57034,7 +57034,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -57052,16 +57052,16 @@
         <v>81</v>
       </c>
       <c r="I8">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>18</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquid Nitrogen</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -57071,7 +57071,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -57089,26 +57089,26 @@
         <v>81</v>
       </c>
       <c r="I9">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquid Nitrogen</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -57126,26 +57126,26 @@
         <v>81</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J10">
-        <v>81</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquid Nitrogen</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -57163,26 +57163,26 @@
         <v>81</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J11">
-        <v>81</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -57200,26 +57200,26 @@
         <v>81</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J12">
-        <v>81</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,26 +57237,26 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="J13">
-        <v>81</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,26 +57274,26 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="J14">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,10 +57311,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J15">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -57325,12 +57325,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57348,26 +57348,26 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">UMUT CAA CELLS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57385,26 +57385,26 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57422,26 +57422,26 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">DUZENLE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -57459,26 +57459,26 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">ONGOING</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -57496,26 +57496,26 @@
         <v>81</v>
       </c>
       <c r="I20">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -57533,26 +57533,26 @@
         <v>81</v>
       </c>
       <c r="I21">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -56950,17 +56950,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -56978,26 +56978,26 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J6">
-        <v>81</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -57015,26 +57015,26 @@
         <v>81</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J7">
-        <v>81</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -57052,26 +57052,26 @@
         <v>81</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J8">
-        <v>81</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -57089,10 +57089,10 @@
         <v>81</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="J9">
-        <v>81</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -57108,7 +57108,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -57126,10 +57126,10 @@
         <v>81</v>
       </c>
       <c r="I10">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -57145,7 +57145,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -57163,10 +57163,10 @@
         <v>81</v>
       </c>
       <c r="I11">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="J11">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -57177,12 +57177,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -57200,26 +57200,26 @@
         <v>81</v>
       </c>
       <c r="I12">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">UMUT CAA CELLS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -57237,26 +57237,26 @@
         <v>81</v>
       </c>
       <c r="I13">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -57274,26 +57274,26 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">DUZENLE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -57311,26 +57311,26 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">ONGOING</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -57367,7 +57367,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CAA CELLS</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -57399,12 +57399,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57431,7 +57431,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -57441,7 +57441,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -57468,7 +57468,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -57478,7 +57478,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONGOING</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -57505,7 +57505,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -57515,7 +57515,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -57542,17 +57542,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -211,7 +211,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -293,7 +293,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -375,7 +375,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -17483,7 +17483,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -17786,7 +17786,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -17863,7 +17863,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -18402,7 +18402,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -18479,7 +18479,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -18556,7 +18556,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -19095,7 +19095,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -20682,7 +20682,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -21186,7 +21186,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -21258,7 +21258,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -21546,7 +21546,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -21690,7 +21690,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -21762,7 +21762,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -21906,7 +21906,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -22122,7 +22122,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -22266,7 +22266,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -22410,7 +22410,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -22693,7 +22693,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -22765,7 +22765,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -22837,7 +22837,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -23125,7 +23125,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -23197,7 +23197,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -23619,7 +23619,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -23835,7 +23835,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -24123,7 +24123,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -24195,7 +24195,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -24267,7 +24267,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
@@ -24411,7 +24411,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
@@ -24478,7 +24478,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -24622,7 +24622,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -24694,7 +24694,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
@@ -24838,7 +24838,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -24910,7 +24910,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -25054,7 +25054,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -25126,7 +25126,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
@@ -25337,7 +25337,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -25409,7 +25409,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -25553,7 +25553,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -26186,7 +26186,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -26258,7 +26258,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
@@ -26330,7 +26330,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
@@ -26402,7 +26402,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -26618,7 +26618,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -26690,7 +26690,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -26968,7 +26968,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
@@ -27035,7 +27035,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -27246,7 +27246,7 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
@@ -27318,7 +27318,7 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
@@ -27390,7 +27390,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -27457,7 +27457,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
@@ -27812,7 +27812,7 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O365" t="inlineStr">
@@ -27884,7 +27884,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
@@ -27956,7 +27956,7 @@
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -28167,7 +28167,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -28311,7 +28311,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
@@ -28450,7 +28450,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -28522,7 +28522,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
@@ -28666,7 +28666,7 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
@@ -28738,7 +28738,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -28882,7 +28882,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -28954,7 +28954,7 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
@@ -29026,7 +29026,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -29098,7 +29098,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
@@ -29170,7 +29170,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
@@ -29242,7 +29242,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
@@ -29386,7 +29386,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O388" t="inlineStr">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
@@ -29602,7 +29602,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
@@ -29674,7 +29674,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
@@ -29746,7 +29746,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
@@ -29818,7 +29818,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O394" t="inlineStr">
@@ -29962,7 +29962,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O395" t="inlineStr">
@@ -30034,7 +30034,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O396" t="inlineStr">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O398" t="inlineStr">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O399" t="inlineStr">
@@ -30322,7 +30322,7 @@
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O400" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O401" t="inlineStr">
@@ -30466,7 +30466,7 @@
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O402" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O403" t="inlineStr">
@@ -30610,7 +30610,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O404" t="inlineStr">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -30754,7 +30754,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
@@ -30826,7 +30826,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -30898,7 +30898,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
@@ -30970,7 +30970,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
@@ -31042,7 +31042,7 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O410" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O411" t="inlineStr">
@@ -31186,7 +31186,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -31258,7 +31258,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O414" t="inlineStr">
@@ -31402,7 +31402,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -31474,7 +31474,7 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O416" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
@@ -31618,7 +31618,7 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O418" t="inlineStr">
@@ -31690,7 +31690,7 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O419" t="inlineStr">
@@ -31762,7 +31762,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O420" t="inlineStr">
@@ -31834,7 +31834,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O421" t="inlineStr">
@@ -31901,7 +31901,7 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O422" t="inlineStr">
@@ -31973,7 +31973,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O423" t="inlineStr">
@@ -32045,7 +32045,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O424" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O425" t="inlineStr">
@@ -32189,7 +32189,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
@@ -32261,7 +32261,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
@@ -32333,7 +32333,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
@@ -32405,7 +32405,7 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
@@ -32477,7 +32477,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O431" t="inlineStr">
@@ -32611,7 +32611,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
@@ -32755,7 +32755,7 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O434" t="inlineStr">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O435" t="inlineStr">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O436" t="inlineStr">
@@ -32971,7 +32971,7 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
@@ -33043,7 +33043,7 @@
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O438" t="inlineStr">
@@ -33115,7 +33115,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
@@ -33182,7 +33182,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O441" t="inlineStr">
@@ -33321,7 +33321,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O442" t="inlineStr">
@@ -33393,7 +33393,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O443" t="inlineStr">
@@ -33465,7 +33465,7 @@
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O444" t="inlineStr">
@@ -33537,7 +33537,7 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
@@ -33609,7 +33609,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -33681,7 +33681,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O447" t="inlineStr">
@@ -33753,7 +33753,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
@@ -33825,7 +33825,7 @@
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O449" t="inlineStr">
@@ -33897,7 +33897,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O450" t="inlineStr">
@@ -33969,7 +33969,7 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O451" t="inlineStr">
@@ -34041,7 +34041,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O452" t="inlineStr">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
@@ -34185,7 +34185,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O454" t="inlineStr">
@@ -34257,7 +34257,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O455" t="inlineStr">
@@ -34329,7 +34329,7 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O456" t="inlineStr">
@@ -34401,7 +34401,7 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O457" t="inlineStr">
@@ -34473,7 +34473,7 @@
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O458" t="inlineStr">
@@ -34545,7 +34545,7 @@
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O459" t="inlineStr">
@@ -34617,7 +34617,7 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O460" t="inlineStr">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O461" t="inlineStr">
@@ -34761,7 +34761,7 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O462" t="inlineStr">
@@ -34833,7 +34833,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -34905,7 +34905,7 @@
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O464" t="inlineStr">
@@ -34977,7 +34977,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -35049,7 +35049,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O466" t="inlineStr">
@@ -35121,7 +35121,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O467" t="inlineStr">
@@ -35193,7 +35193,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O468" t="inlineStr">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O469" t="inlineStr">
@@ -35337,7 +35337,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
@@ -35409,7 +35409,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
@@ -35481,7 +35481,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
@@ -35553,7 +35553,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
@@ -35625,7 +35625,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
@@ -35697,7 +35697,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
@@ -35769,7 +35769,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
@@ -35841,7 +35841,7 @@
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O477" t="inlineStr">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
@@ -35985,7 +35985,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
@@ -36057,7 +36057,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O481" t="inlineStr">
@@ -36201,7 +36201,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O482" t="inlineStr">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -36345,7 +36345,7 @@
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O484" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O485" t="inlineStr">
@@ -36489,7 +36489,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
@@ -36561,7 +36561,7 @@
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O487" t="inlineStr">
@@ -36633,7 +36633,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
@@ -36705,7 +36705,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
@@ -36777,7 +36777,7 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O490" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O491" t="inlineStr">
@@ -36921,7 +36921,7 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
@@ -36993,7 +36993,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O493" t="inlineStr">
@@ -37065,7 +37065,7 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O494" t="inlineStr">
@@ -37137,7 +37137,7 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O495" t="inlineStr">
@@ -37209,7 +37209,7 @@
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O496" t="inlineStr">
@@ -37281,7 +37281,7 @@
       </c>
       <c r="N497" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O497" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O498" t="inlineStr">
@@ -37425,7 +37425,7 @@
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O499" t="inlineStr">
@@ -37497,7 +37497,7 @@
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O500" t="inlineStr">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O501" t="inlineStr">
@@ -37641,7 +37641,7 @@
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O502" t="inlineStr">
@@ -37723,7 +37723,7 @@
       </c>
       <c r="N503" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O503" t="inlineStr">
@@ -37800,7 +37800,7 @@
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O504" t="inlineStr">
@@ -37877,7 +37877,7 @@
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O505" t="inlineStr">
@@ -37959,7 +37959,7 @@
       </c>
       <c r="N506" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O506" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O507" t="inlineStr">
@@ -38123,7 +38123,7 @@
       </c>
       <c r="N508" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O508" t="inlineStr">
@@ -38205,7 +38205,7 @@
       </c>
       <c r="N509" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O509" t="inlineStr">
@@ -38287,7 +38287,7 @@
       </c>
       <c r="N510" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O510" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="N511" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O511" t="inlineStr">
@@ -38451,7 +38451,7 @@
       </c>
       <c r="N512" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O512" t="inlineStr">
@@ -38533,7 +38533,7 @@
       </c>
       <c r="N513" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O513" t="inlineStr">
@@ -38615,7 +38615,7 @@
       </c>
       <c r="N514" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O514" t="inlineStr">
@@ -38697,7 +38697,7 @@
       </c>
       <c r="N515" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O515" t="inlineStr">
@@ -38779,7 +38779,7 @@
       </c>
       <c r="N516" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O516" t="inlineStr">
@@ -38826,7 +38826,7 @@
       </c>
       <c r="N517" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O517" t="inlineStr">
@@ -38873,7 +38873,7 @@
       </c>
       <c r="N518" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O518" t="inlineStr">
@@ -38920,7 +38920,7 @@
       </c>
       <c r="N519" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O519" t="inlineStr">
@@ -38967,7 +38967,7 @@
       </c>
       <c r="N520" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O520" t="inlineStr">
@@ -39014,7 +39014,7 @@
       </c>
       <c r="N521" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O521" t="inlineStr">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="N522" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O522" t="inlineStr">
@@ -39108,7 +39108,7 @@
       </c>
       <c r="N523" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O523" t="inlineStr">
@@ -39155,7 +39155,7 @@
       </c>
       <c r="N524" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O524" t="inlineStr">
@@ -39202,7 +39202,7 @@
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O525" t="inlineStr">
@@ -39249,7 +39249,7 @@
       </c>
       <c r="N526" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O526" t="inlineStr">
@@ -39296,7 +39296,7 @@
       </c>
       <c r="N527" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O527" t="inlineStr">
@@ -39343,7 +39343,7 @@
       </c>
       <c r="N528" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O528" t="inlineStr">
@@ -39390,7 +39390,7 @@
       </c>
       <c r="N529" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O529" t="inlineStr">
@@ -39437,7 +39437,7 @@
       </c>
       <c r="N530" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O530" t="inlineStr">
@@ -39484,7 +39484,7 @@
       </c>
       <c r="N531" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O531" t="inlineStr">
@@ -39531,7 +39531,7 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O532" t="inlineStr">
@@ -39578,7 +39578,7 @@
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O533" t="inlineStr">
@@ -39625,7 +39625,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O534" t="inlineStr">
@@ -39672,7 +39672,7 @@
       </c>
       <c r="N535" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O535" t="inlineStr">
@@ -39719,7 +39719,7 @@
       </c>
       <c r="N536" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O536" t="inlineStr">
@@ -39766,7 +39766,7 @@
       </c>
       <c r="N537" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O537" t="inlineStr">
@@ -39813,7 +39813,7 @@
       </c>
       <c r="N538" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O538" t="inlineStr">
@@ -39860,7 +39860,7 @@
       </c>
       <c r="N539" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O539" t="inlineStr">
@@ -39907,7 +39907,7 @@
       </c>
       <c r="N540" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O540" t="inlineStr">
@@ -39954,7 +39954,7 @@
       </c>
       <c r="N541" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O541" t="inlineStr">
@@ -40001,7 +40001,7 @@
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O542" t="inlineStr">
@@ -40048,7 +40048,7 @@
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O543" t="inlineStr">
@@ -40095,7 +40095,7 @@
       </c>
       <c r="N544" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O544" t="inlineStr">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="N545" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O545" t="inlineStr">
@@ -40189,7 +40189,7 @@
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O546" t="inlineStr">
@@ -40236,7 +40236,7 @@
       </c>
       <c r="N547" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O547" t="inlineStr">
@@ -40283,7 +40283,7 @@
       </c>
       <c r="N548" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O548" t="inlineStr">
@@ -40330,7 +40330,7 @@
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O549" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O550" t="inlineStr">
@@ -40424,7 +40424,7 @@
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O551" t="inlineStr">
@@ -40471,7 +40471,7 @@
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O552" t="inlineStr">
@@ -40518,7 +40518,7 @@
       </c>
       <c r="N553" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O553" t="inlineStr">
@@ -40565,7 +40565,7 @@
       </c>
       <c r="N554" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O554" t="inlineStr">
@@ -40612,7 +40612,7 @@
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O555" t="inlineStr">
@@ -40659,7 +40659,7 @@
       </c>
       <c r="N556" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O556" t="inlineStr">
@@ -40706,7 +40706,7 @@
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O557" t="inlineStr">
@@ -40753,7 +40753,7 @@
       </c>
       <c r="N558" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O558" t="inlineStr">
@@ -40800,7 +40800,7 @@
       </c>
       <c r="N559" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O559" t="inlineStr">
@@ -40847,7 +40847,7 @@
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O560" t="inlineStr">
@@ -40894,7 +40894,7 @@
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O561" t="inlineStr">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="N562" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O562" t="inlineStr">
@@ -40988,7 +40988,7 @@
       </c>
       <c r="N563" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O563" t="inlineStr">
@@ -41035,7 +41035,7 @@
       </c>
       <c r="N564" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O564" t="inlineStr">
@@ -41082,7 +41082,7 @@
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O565" t="inlineStr">
@@ -41129,7 +41129,7 @@
       </c>
       <c r="N566" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O566" t="inlineStr">
@@ -41176,7 +41176,7 @@
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O567" t="inlineStr">
@@ -41223,7 +41223,7 @@
       </c>
       <c r="N568" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O568" t="inlineStr">
@@ -41270,7 +41270,7 @@
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O569" t="inlineStr">
@@ -41317,7 +41317,7 @@
       </c>
       <c r="N570" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O570" t="inlineStr">
@@ -41364,7 +41364,7 @@
       </c>
       <c r="N571" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O571" t="inlineStr">
@@ -41411,7 +41411,7 @@
       </c>
       <c r="N572" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O572" t="inlineStr">
@@ -41458,7 +41458,7 @@
       </c>
       <c r="N573" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O573" t="inlineStr">
@@ -41505,7 +41505,7 @@
       </c>
       <c r="N574" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O574" t="inlineStr">
@@ -41552,7 +41552,7 @@
       </c>
       <c r="N575" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O575" t="inlineStr">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="N576" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O576" t="inlineStr">
@@ -41646,7 +41646,7 @@
       </c>
       <c r="N577" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O577" t="inlineStr">
@@ -41693,7 +41693,7 @@
       </c>
       <c r="N578" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O578" t="inlineStr">
@@ -41740,7 +41740,7 @@
       </c>
       <c r="N579" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O579" t="inlineStr">
@@ -41787,7 +41787,7 @@
       </c>
       <c r="N580" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O580" t="inlineStr">
@@ -41834,7 +41834,7 @@
       </c>
       <c r="N581" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O581" t="inlineStr">
@@ -41881,7 +41881,7 @@
       </c>
       <c r="N582" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O582" t="inlineStr">
@@ -41928,7 +41928,7 @@
       </c>
       <c r="N583" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O583" t="inlineStr">
@@ -41975,7 +41975,7 @@
       </c>
       <c r="N584" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O584" t="inlineStr">
@@ -42022,7 +42022,7 @@
       </c>
       <c r="N585" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O585" t="inlineStr">
@@ -42069,7 +42069,7 @@
       </c>
       <c r="N586" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O586" t="inlineStr">
@@ -42116,7 +42116,7 @@
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O587" t="inlineStr">
@@ -42163,7 +42163,7 @@
       </c>
       <c r="N588" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O588" t="inlineStr">
@@ -42210,7 +42210,7 @@
       </c>
       <c r="N589" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O589" t="inlineStr">
@@ -42257,7 +42257,7 @@
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O590" t="inlineStr">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O591" t="inlineStr">
@@ -42351,7 +42351,7 @@
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O592" t="inlineStr">
@@ -42398,7 +42398,7 @@
       </c>
       <c r="N593" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O593" t="inlineStr">
@@ -42445,7 +42445,7 @@
       </c>
       <c r="N594" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O594" t="inlineStr">
@@ -42492,7 +42492,7 @@
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O595" t="inlineStr">
@@ -42539,7 +42539,7 @@
       </c>
       <c r="N596" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O596" t="inlineStr">
@@ -42586,7 +42586,7 @@
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O597" t="inlineStr">
@@ -42633,7 +42633,7 @@
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
@@ -42680,7 +42680,7 @@
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
@@ -42727,7 +42727,7 @@
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
@@ -42774,7 +42774,7 @@
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
@@ -42821,7 +42821,7 @@
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
@@ -42868,7 +42868,7 @@
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
@@ -42915,7 +42915,7 @@
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O604" t="inlineStr">
@@ -42962,7 +42962,7 @@
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
@@ -43009,7 +43009,7 @@
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
@@ -43056,7 +43056,7 @@
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O607" t="inlineStr">
@@ -43103,7 +43103,7 @@
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
@@ -43150,7 +43150,7 @@
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O609" t="inlineStr">
@@ -43197,7 +43197,7 @@
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O610" t="inlineStr">
@@ -43244,7 +43244,7 @@
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O611" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O612" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O613" t="inlineStr">
@@ -43385,7 +43385,7 @@
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O614" t="inlineStr">
@@ -43432,7 +43432,7 @@
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O615" t="inlineStr">
@@ -43479,7 +43479,7 @@
       </c>
       <c r="N616" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O616" t="inlineStr">
@@ -43526,7 +43526,7 @@
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O617" t="inlineStr">
@@ -43573,7 +43573,7 @@
       </c>
       <c r="N618" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O618" t="inlineStr">
@@ -43620,7 +43620,7 @@
       </c>
       <c r="N619" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O619" t="inlineStr">
@@ -43667,7 +43667,7 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O620" t="inlineStr">
@@ -43714,7 +43714,7 @@
       </c>
       <c r="N621" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O621" t="inlineStr">
@@ -43761,7 +43761,7 @@
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O622" t="inlineStr">
@@ -43808,7 +43808,7 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O623" t="inlineStr">
@@ -43855,7 +43855,7 @@
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O624" t="inlineStr">
@@ -43902,7 +43902,7 @@
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O625" t="inlineStr">
@@ -43949,7 +43949,7 @@
       </c>
       <c r="N626" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O626" t="inlineStr">
@@ -43996,7 +43996,7 @@
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O627" t="inlineStr">
@@ -44043,7 +44043,7 @@
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O628" t="inlineStr">
@@ -44090,7 +44090,7 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O629" t="inlineStr">
@@ -44137,7 +44137,7 @@
       </c>
       <c r="N630" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O630" t="inlineStr">
@@ -44184,7 +44184,7 @@
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O631" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="N632" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O632" t="inlineStr">
@@ -44278,7 +44278,7 @@
       </c>
       <c r="N633" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O633" t="inlineStr">
@@ -44325,7 +44325,7 @@
       </c>
       <c r="N634" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O634" t="inlineStr">
@@ -44372,7 +44372,7 @@
       </c>
       <c r="N635" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O635" t="inlineStr">
@@ -44419,7 +44419,7 @@
       </c>
       <c r="N636" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O636" t="inlineStr">
@@ -44466,7 +44466,7 @@
       </c>
       <c r="N637" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O637" t="inlineStr">
@@ -44513,7 +44513,7 @@
       </c>
       <c r="N638" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O638" t="inlineStr">
@@ -44560,7 +44560,7 @@
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O639" t="inlineStr">
@@ -44607,7 +44607,7 @@
       </c>
       <c r="N640" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
@@ -44654,7 +44654,7 @@
       </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
@@ -44701,7 +44701,7 @@
       </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
@@ -44748,7 +44748,7 @@
       </c>
       <c r="N643" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O643" t="inlineStr">
@@ -44795,7 +44795,7 @@
       </c>
       <c r="N644" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O644" t="inlineStr">
@@ -44842,7 +44842,7 @@
       </c>
       <c r="N645" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
@@ -44889,7 +44889,7 @@
       </c>
       <c r="N646" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
@@ -44936,7 +44936,7 @@
       </c>
       <c r="N647" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
@@ -44983,7 +44983,7 @@
       </c>
       <c r="N648" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O648" t="inlineStr">
@@ -45030,7 +45030,7 @@
       </c>
       <c r="N649" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57399,12 +57399,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">Umut Cell Box -5-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -57431,17 +57431,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -57478,7 +57478,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -57515,7 +57515,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -57552,7 +57552,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -57579,17 +57579,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unkown FOR NOW</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -57626,7 +57626,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">No use</t>
+          <t xml:space="preserve">Unkown FOR NOW</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -57647,6 +57647,43 @@
         <v>0</v>
       </c>
       <c r="J24">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No use</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>9</v>
+      </c>
+      <c r="G25">
+        <v>9</v>
+      </c>
+      <c r="H25">
+        <v>81</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>81</v>
       </c>
     </row>

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57687,6 +57687,43 @@
         <v>81</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Big Plasmid Box</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>9</v>
+      </c>
+      <c r="H26">
+        <v>81</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57436,12 +57436,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">Big Plasmid Box</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -57468,17 +57468,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -57515,7 +57515,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -57552,7 +57552,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -57589,7 +57589,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -57616,17 +57616,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unkown FOR NOW</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -57663,7 +57663,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">No use</t>
+          <t xml:space="preserve">Unkown FOR NOW</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -57700,7 +57700,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Plasmid Box</t>
+          <t xml:space="preserve">No use</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
